--- a/anotacion/anotacion_A1.xlsx
+++ b/anotacion/anotacion_A1.xlsx
@@ -2,16 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20100" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCCIONES" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ANOTACION" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -27,19 +26,28 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="4">
@@ -51,12 +59,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002A78D6"/>
+        <fgColor rgb="FF2A78D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EFEFEA"/>
+        <fgColor rgb="FFEFEFEA"/>
       </patternFill>
     </fill>
   </fills>
@@ -87,7 +95,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -451,12 +459,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="95" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="16" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Anotación de sentimiento · Analítica Educativa</t>
@@ -464,7 +472,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -474,7 +482,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
+      <c r="A4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -526,7 +534,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
+      <c r="A12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -557,7 +565,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr"/>
+      <c r="A17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -584,8 +592,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H252"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H250"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
@@ -639,7 +647,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="16" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -658,14 +666,18 @@
           <t>Es uno de los mejores profesores de aiub.</t>
         </is>
       </c>
-      <c r="E2" s="7" t="n"/>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F2" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="7" t="n"/>
       <c r="H2" s="7" t="n"/>
     </row>
-    <row r="3">
+    <row r="3" ht="16" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -684,14 +696,18 @@
           <t>Todos los demás están bien.</t>
         </is>
       </c>
-      <c r="E3" s="7" t="n"/>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F3" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="7" t="n"/>
       <c r="H3" s="7" t="n"/>
     </row>
-    <row r="4">
+    <row r="4" ht="16" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -710,14 +726,22 @@
           <t>Un buen profesor</t>
         </is>
       </c>
-      <c r="E4" s="7" t="n"/>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F4" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="7" t="n"/>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>muy_corto</t>
+        </is>
+      </c>
       <c r="H4" s="7" t="n"/>
     </row>
-    <row r="5">
+    <row r="5" ht="32" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -736,14 +760,22 @@
           <t>Es nueva, así que necesita mucho más tiempo para familiarizarse con la enseñanza.</t>
         </is>
       </c>
-      <c r="E5" s="7" t="n"/>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>critica_suave</t>
+        </is>
+      </c>
       <c r="H5" s="7" t="n"/>
     </row>
-    <row r="6">
+    <row r="6" ht="16" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -762,14 +794,22 @@
           <t>¡Nadie puede preguntarle nada!</t>
         </is>
       </c>
-      <c r="E6" s="7" t="n"/>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="7" t="n"/>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>muy_corto</t>
+        </is>
+      </c>
       <c r="H6" s="7" t="n"/>
     </row>
-    <row r="7">
+    <row r="7" ht="16" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -788,14 +828,22 @@
           <t>Buen profesor.</t>
         </is>
       </c>
-      <c r="E7" s="7" t="n"/>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F7" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="7" t="n"/>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>muy_corto</t>
+        </is>
+      </c>
       <c r="H7" s="7" t="n"/>
     </row>
-    <row r="8">
+    <row r="8" ht="16" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -814,14 +862,22 @@
           <t>Desempeño sobresaliente.</t>
         </is>
       </c>
-      <c r="E8" s="7" t="n"/>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F8" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="7" t="n"/>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>muy_corto</t>
+        </is>
+      </c>
       <c r="H8" s="7" t="n"/>
     </row>
-    <row r="9">
+    <row r="9" ht="16" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -840,14 +896,22 @@
           <t>El profesor tiene buen conocimiento de la materia y es comprensible.</t>
         </is>
       </c>
-      <c r="E9" s="7" t="n"/>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="7" t="n"/>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>descriptivo</t>
+        </is>
+      </c>
       <c r="H9" s="7" t="n"/>
     </row>
-    <row r="10">
+    <row r="10" ht="32" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -866,14 +930,22 @@
           <t>Es un buen profesor, pero no es atento con los estudiantes más flojos. Debería dar más tiempo a los estudiantes para entender su clase.</t>
         </is>
       </c>
-      <c r="E10" s="7" t="n"/>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>critica_suave</t>
+        </is>
+      </c>
       <c r="H10" s="7" t="n"/>
     </row>
-    <row r="11">
+    <row r="11" ht="16" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -892,14 +964,22 @@
           <t>Debería ser más abierto con los estudiantes en cuanto a la enseñanza.</t>
         </is>
       </c>
-      <c r="E11" s="7" t="n"/>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F11" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="7" t="n"/>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>critica_suave</t>
+        </is>
+      </c>
       <c r="H11" s="7" t="n"/>
     </row>
-    <row r="12">
+    <row r="12" ht="16" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -918,14 +998,22 @@
           <t>Es una profesora agradable, además de muy estricta y amable.</t>
         </is>
       </c>
-      <c r="E12" s="7" t="n"/>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F12" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="7" t="n"/>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>descriptivo</t>
+        </is>
+      </c>
       <c r="H12" s="7" t="n"/>
     </row>
-    <row r="13">
+    <row r="13" ht="16" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -944,14 +1032,18 @@
           <t>Es un profesor realmente bueno para los estudiantes.</t>
         </is>
       </c>
-      <c r="E13" s="7" t="n"/>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="7" t="n"/>
       <c r="H13" s="7" t="n"/>
     </row>
-    <row r="14">
+    <row r="14" ht="16" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -970,14 +1062,18 @@
           <t>Necesita ir un poco más despacio al dar la clase.</t>
         </is>
       </c>
-      <c r="E14" s="7" t="n"/>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F14" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="7" t="n"/>
       <c r="H14" s="7" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" ht="16" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -996,14 +1092,18 @@
           <t>Su cara agradable y alegre es notable. Buen profesor.</t>
         </is>
       </c>
-      <c r="E15" s="7" t="n"/>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="7" t="n"/>
       <c r="H15" s="7" t="n"/>
     </row>
-    <row r="16">
+    <row r="16" ht="16" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -1022,14 +1122,22 @@
           <t>Es un profesor ideal, pero tiene que hacer su sistema de enseñanza más fácil.</t>
         </is>
       </c>
-      <c r="E16" s="7" t="n"/>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>critica_suave</t>
+        </is>
+      </c>
       <c r="H16" s="7" t="n"/>
     </row>
-    <row r="17">
+    <row r="17" ht="16" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -1048,14 +1156,22 @@
           <t>Tiene buen dominio.</t>
         </is>
       </c>
-      <c r="E17" s="7" t="n"/>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F17" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G17" s="7" t="n"/>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>muy_corto</t>
+        </is>
+      </c>
       <c r="H17" s="7" t="n"/>
     </row>
-    <row r="18">
+    <row r="18" ht="16" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -1074,14 +1190,22 @@
           <t>es un excelente profesor.</t>
         </is>
       </c>
-      <c r="E18" s="7" t="n"/>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F18" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G18" s="7" t="n"/>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>muy_corto</t>
+        </is>
+      </c>
       <c r="H18" s="7" t="n"/>
     </row>
-    <row r="19">
+    <row r="19" ht="16" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -1100,14 +1224,18 @@
           <t>creo que es realmente perfecto para dictar el laboratorio de a.c</t>
         </is>
       </c>
-      <c r="E19" s="7" t="n"/>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F19" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="7" t="n"/>
       <c r="H19" s="7" t="n"/>
     </row>
-    <row r="20">
+    <row r="20" ht="16" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -1126,14 +1254,22 @@
           <t>Buenos modales.</t>
         </is>
       </c>
-      <c r="E20" s="7" t="n"/>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F20" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="7" t="n"/>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>muy_corto</t>
+        </is>
+      </c>
       <c r="H20" s="7" t="n"/>
     </row>
-    <row r="21">
+    <row r="21" ht="16" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -1152,14 +1288,22 @@
           <t>Responsable.</t>
         </is>
       </c>
-      <c r="E21" s="7" t="n"/>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F21" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G21" s="7" t="n"/>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>muy_corto</t>
+        </is>
+      </c>
       <c r="H21" s="7" t="n"/>
     </row>
-    <row r="22">
+    <row r="22" ht="16" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -1178,14 +1322,22 @@
           <t>muy buen profesor y ante todo sincero</t>
         </is>
       </c>
-      <c r="E22" s="7" t="n"/>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F22" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G22" s="7" t="n"/>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>muy_corto</t>
+        </is>
+      </c>
       <c r="H22" s="7" t="n"/>
     </row>
-    <row r="23">
+    <row r="23" ht="16" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -1204,14 +1356,18 @@
           <t>El profesor más equilibrado que he visto</t>
         </is>
       </c>
-      <c r="E23" s="7" t="n"/>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F23" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="7" t="n"/>
       <c r="H23" s="7" t="n"/>
     </row>
-    <row r="24">
+    <row r="24" ht="16" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -1230,14 +1386,18 @@
           <t>Es extraordinario.</t>
         </is>
       </c>
-      <c r="E24" s="7" t="n"/>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F24" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="7" t="n"/>
     </row>
-    <row r="25">
+    <row r="25" ht="32" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -1256,14 +1416,18 @@
           <t>A veces él mismo no tiene claro lo que está enseñando. Para mí no es suficientemente bueno.</t>
         </is>
       </c>
-      <c r="E25" s="7" t="n"/>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F25" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="7" t="n"/>
     </row>
-    <row r="26">
+    <row r="26" ht="16" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -1282,14 +1446,18 @@
           <t>Debe mejorar como profesor.</t>
         </is>
       </c>
-      <c r="E26" s="7" t="n"/>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F26" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G26" s="7" t="n"/>
       <c r="H26" s="7" t="n"/>
     </row>
-    <row r="27">
+    <row r="27" ht="16" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -1308,14 +1476,18 @@
           <t>La clase es muy aburrida y monótona.</t>
         </is>
       </c>
-      <c r="E27" s="7" t="n"/>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F27" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="7" t="n"/>
       <c r="H27" s="7" t="n"/>
     </row>
-    <row r="28">
+    <row r="28" ht="16" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -1334,14 +1506,18 @@
           <t>no dio puntos parciales</t>
         </is>
       </c>
-      <c r="E28" s="7" t="n"/>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F28" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G28" s="7" t="n"/>
       <c r="H28" s="7" t="n"/>
     </row>
-    <row r="29">
+    <row r="29" ht="16" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -1360,14 +1536,18 @@
           <t>Bueno, debería dedicar más tiempo a ciertos puntos relacionados con la clase.</t>
         </is>
       </c>
-      <c r="E29" s="7" t="n"/>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F29" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="7" t="n"/>
       <c r="H29" s="7" t="n"/>
     </row>
-    <row r="30">
+    <row r="30" ht="16" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -1386,14 +1566,22 @@
           <t>Es regular. Solo regular.</t>
         </is>
       </c>
-      <c r="E30" s="7" t="n"/>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H30" s="7" t="n"/>
     </row>
-    <row r="31">
+    <row r="31" ht="32" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -1412,14 +1600,22 @@
           <t>Nuestro respetable profesor. Habla bastante rápido, con énfasis, de modo que a veces no entendemos lo que quiere decir. Es bueno.</t>
         </is>
       </c>
-      <c r="E31" s="7" t="n"/>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F31" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H31" s="7" t="n"/>
     </row>
-    <row r="32">
+    <row r="32" ht="16" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -1438,14 +1634,18 @@
           <t>creo que es una buena profesora. Su método de enseñanza es bueno.</t>
         </is>
       </c>
-      <c r="E32" s="7" t="n"/>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F32" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G32" s="7" t="n"/>
       <c r="H32" s="7" t="n"/>
     </row>
-    <row r="33">
+    <row r="33" ht="16" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -1464,14 +1664,18 @@
           <t>Muy mal profesor.</t>
         </is>
       </c>
-      <c r="E33" s="7" t="n"/>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F33" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G33" s="7" t="n"/>
       <c r="H33" s="7" t="n"/>
     </row>
-    <row r="34">
+    <row r="34" ht="16" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -1490,14 +1694,18 @@
           <t>Es buena, pero debería ser más moderada al poner notas.</t>
         </is>
       </c>
-      <c r="E34" s="7" t="n"/>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F34" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="7" t="n"/>
       <c r="H34" s="7" t="n"/>
     </row>
-    <row r="35">
+    <row r="35" ht="64" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -1516,14 +1724,18 @@
           <t>un docente excelente. de verdad hace que el estudiante entienda muy bien en clase. después de entender, nuestro concepto queda absolutamente claro. da excelentes ejemplos relacionados con el mundo real para hacernos entender un tema. hace la clase muy interesante. en general, un docente excelente.</t>
         </is>
       </c>
-      <c r="E35" s="7" t="n"/>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F35" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G35" s="7" t="n"/>
       <c r="H35" s="7" t="n"/>
     </row>
-    <row r="36">
+    <row r="36" ht="16" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -1542,14 +1754,18 @@
           <t>No es un buen profesor.</t>
         </is>
       </c>
-      <c r="E36" s="7" t="n"/>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F36" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="7" t="n"/>
       <c r="H36" s="7" t="n"/>
     </row>
-    <row r="37">
+    <row r="37" ht="16" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -1568,14 +1784,18 @@
           <t>Es honesto conmigo.</t>
         </is>
       </c>
-      <c r="E37" s="7" t="n"/>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F37" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G37" s="7" t="n"/>
       <c r="H37" s="7" t="n"/>
     </row>
-    <row r="38">
+    <row r="38" ht="16" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -1594,14 +1814,18 @@
           <t>Bueno y cuidadoso.</t>
         </is>
       </c>
-      <c r="E38" s="7" t="n"/>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F38" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="7" t="n"/>
       <c r="H38" s="7" t="n"/>
     </row>
-    <row r="39">
+    <row r="39" ht="16" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -1620,14 +1844,22 @@
           <t>Siempre nos da tareas todo el tiempo, pero nos ensena un curso corto.</t>
         </is>
       </c>
-      <c r="E39" s="7" t="n"/>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F39" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>muy_corto</t>
+        </is>
+      </c>
       <c r="H39" s="7" t="n"/>
     </row>
-    <row r="40">
+    <row r="40" ht="16" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -1646,14 +1878,18 @@
           <t>El maestro más divertido y con más personalidad que he visto.</t>
         </is>
       </c>
-      <c r="E40" s="7" t="n"/>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F40" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G40" s="7" t="n"/>
       <c r="H40" s="7" t="n"/>
     </row>
-    <row r="41">
+    <row r="41" ht="16" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -1672,14 +1908,18 @@
           <t>Es cooperativa</t>
         </is>
       </c>
-      <c r="E41" s="7" t="n"/>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F41" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G41" s="7" t="n"/>
       <c r="H41" s="7" t="n"/>
     </row>
-    <row r="42">
+    <row r="42" ht="48" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -1698,14 +1938,18 @@
           <t>Un profesor que trata de preparar a los estudiantes para enfrentar la vida practica o profesional de forma independiente. Gracias tanto al profesor como a la administracion de la universidad.</t>
         </is>
       </c>
-      <c r="E42" s="7" t="n"/>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F42" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G42" s="7" t="n"/>
       <c r="H42" s="7" t="n"/>
     </row>
-    <row r="43">
+    <row r="43" ht="32" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -1724,14 +1968,18 @@
           <t>Su estilo de enseñanza no es muy bueno y los estudiantes no sienten interés por esta materia.</t>
         </is>
       </c>
-      <c r="E43" s="7" t="n"/>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F43" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G43" s="7" t="n"/>
       <c r="H43" s="7" t="n"/>
     </row>
-    <row r="44">
+    <row r="44" ht="32" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -1750,14 +1998,22 @@
           <t>El Sr. Mujibur Rahman es un buen profesor, aunque los estudiantes más lentos podrían encontrarlo un poco demasiado rápido.</t>
         </is>
       </c>
-      <c r="E44" s="7" t="n"/>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>critica_suave</t>
+        </is>
+      </c>
       <c r="H44" s="7" t="n"/>
     </row>
-    <row r="45">
+    <row r="45" ht="16" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -1776,14 +2032,18 @@
           <t>Es muy buen profesor.</t>
         </is>
       </c>
-      <c r="E45" s="7" t="n"/>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F45" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G45" s="7" t="n"/>
       <c r="H45" s="7" t="n"/>
     </row>
-    <row r="46">
+    <row r="46" ht="16" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -1802,14 +2062,18 @@
           <t>La clase es muy dinámica y entretenida.</t>
         </is>
       </c>
-      <c r="E46" s="7" t="n"/>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F46" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G46" s="7" t="n"/>
       <c r="H46" s="7" t="n"/>
     </row>
-    <row r="47">
+    <row r="47" ht="48" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -1828,14 +2092,22 @@
           <t>Uno de mis profesores favoritos. Me gusta asistir a cada una de sus clases. Me gusta su método de enseñanza. Especialmente me gustan los trabajos en grupo que nos da en clase y que de verdad nos ayudan.</t>
         </is>
       </c>
-      <c r="E47" s="7" t="n"/>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F47" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G47" s="7" t="n"/>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>descriptivo</t>
+        </is>
+      </c>
       <c r="H47" s="7" t="n"/>
     </row>
-    <row r="48">
+    <row r="48" ht="32" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -1854,14 +2126,18 @@
           <t>Es un muy buen profesor, pero a veces te tomas demasiado en serio cosas simples.</t>
         </is>
       </c>
-      <c r="E48" s="7" t="n"/>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F48" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G48" s="7" t="n"/>
       <c r="H48" s="7" t="n"/>
     </row>
-    <row r="49">
+    <row r="49" ht="16" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -1880,14 +2156,22 @@
           <t>No.</t>
         </is>
       </c>
-      <c r="E49" s="7" t="n"/>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F49" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G49" s="7" t="n"/>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>sin_sentido</t>
+        </is>
+      </c>
       <c r="H49" s="7" t="n"/>
     </row>
-    <row r="50">
+    <row r="50" ht="16" customHeight="1">
       <c r="A50" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -1906,14 +2190,18 @@
           <t>es un buen profesor y muy divertido. lo único es que se ríe demasiado en clase.</t>
         </is>
       </c>
-      <c r="E50" s="7" t="n"/>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F50" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G50" s="7" t="n"/>
       <c r="H50" s="7" t="n"/>
     </row>
-    <row r="51">
+    <row r="51" ht="32" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -1932,14 +2220,22 @@
           <t>Bienvenido y felicidades. Espero que nos esperen mejores empleos. Buena suerte, profesor, y cuídese.</t>
         </is>
       </c>
-      <c r="E51" s="7" t="n"/>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F51" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G51" s="7" t="n"/>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>sin_sentido</t>
+        </is>
+      </c>
       <c r="H51" s="7" t="n"/>
     </row>
-    <row r="52">
+    <row r="52" ht="16" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -1958,14 +2254,18 @@
           <t>Es un profesor excelente. Espero que la universidad lo trate como corresponde.</t>
         </is>
       </c>
-      <c r="E52" s="7" t="n"/>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F52" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G52" s="7" t="n"/>
       <c r="H52" s="7" t="n"/>
     </row>
-    <row r="53">
+    <row r="53" ht="32" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -1984,14 +2284,18 @@
           <t>Tiene conocimientos y experiencia excepcionales sobre arquitectura. Ilustra con ejemplos. Como profesor, es muy franco y abierto con los estudiantes.</t>
         </is>
       </c>
-      <c r="E53" s="7" t="n"/>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F53" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G53" s="7" t="n"/>
       <c r="H53" s="7" t="n"/>
     </row>
-    <row r="54">
+    <row r="54" ht="16" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -2010,14 +2314,18 @@
           <t>Necesita saber cómo enseñar a los estudiantes.</t>
         </is>
       </c>
-      <c r="E54" s="7" t="n"/>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F54" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G54" s="7" t="n"/>
       <c r="H54" s="7" t="n"/>
     </row>
-    <row r="55">
+    <row r="55" ht="32" customHeight="1">
       <c r="A55" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -2036,14 +2344,18 @@
           <t>Es bueno. Tiene algo en su actitud que realmente ayuda al estudiante a mantenerse en clase. Buen profesor.</t>
         </is>
       </c>
-      <c r="E55" s="7" t="n"/>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F55" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G55" s="7" t="n"/>
       <c r="H55" s="7" t="n"/>
     </row>
-    <row r="56">
+    <row r="56" ht="16" customHeight="1">
       <c r="A56" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -2062,14 +2374,18 @@
           <t>Profesor respetable.</t>
         </is>
       </c>
-      <c r="E56" s="7" t="n"/>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F56" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G56" s="7" t="n"/>
       <c r="H56" s="7" t="n"/>
     </row>
-    <row r="57">
+    <row r="57" ht="48" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -2088,14 +2404,18 @@
           <t>Es experimentado, pero es un perdedor. Además es una persona habladora. No tiene ninguna simpatía por los estudiantes hombres, pero tiene predilección por las estudiantes mujeres.</t>
         </is>
       </c>
-      <c r="E57" s="7" t="n"/>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F57" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G57" s="7" t="n"/>
       <c r="H57" s="7" t="n"/>
     </row>
-    <row r="58">
+    <row r="58" ht="16" customHeight="1">
       <c r="A58" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -2114,14 +2434,18 @@
           <t>Es muy, muy estricta.</t>
         </is>
       </c>
-      <c r="E58" s="7" t="n"/>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F58" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G58" s="7" t="n"/>
       <c r="H58" s="7" t="n"/>
     </row>
-    <row r="59">
+    <row r="59" ht="32" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -2140,14 +2464,18 @@
           <t>No entendemos lo que nos quiere enseñar. Tarda mucho tiempo en hacer entender cualquier cosa.</t>
         </is>
       </c>
-      <c r="E59" s="7" t="n"/>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F59" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G59" s="7" t="n"/>
       <c r="H59" s="7" t="n"/>
     </row>
-    <row r="60">
+    <row r="60" ht="16" customHeight="1">
       <c r="A60" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -2166,14 +2494,18 @@
           <t>No explica bien, me siento perdido.</t>
         </is>
       </c>
-      <c r="E60" s="7" t="n"/>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F60" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G60" s="7" t="n"/>
       <c r="H60" s="7" t="n"/>
     </row>
-    <row r="61">
+    <row r="61" ht="16" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -2192,14 +2524,18 @@
           <t>No tiene habilidad para enseñar. Solo tiene un conocimiento memorizado.</t>
         </is>
       </c>
-      <c r="E61" s="7" t="n"/>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F61" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G61" s="7" t="n"/>
       <c r="H61" s="7" t="n"/>
     </row>
-    <row r="62">
+    <row r="62" ht="16" customHeight="1">
       <c r="A62" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -2218,14 +2554,22 @@
           <t>Es un profesor muy agradable, pero es muy duro con el sistema de calificación.</t>
         </is>
       </c>
-      <c r="E62" s="7" t="n"/>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F62" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>elogio_tibio</t>
+        </is>
+      </c>
       <c r="H62" s="7" t="n"/>
     </row>
-    <row r="63">
+    <row r="63" ht="16" customHeight="1">
       <c r="A63" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -2244,14 +2588,18 @@
           <t>Es un buen profesor.</t>
         </is>
       </c>
-      <c r="E63" s="7" t="n"/>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F63" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G63" s="7" t="n"/>
       <c r="H63" s="7" t="n"/>
     </row>
-    <row r="64">
+    <row r="64" ht="16" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -2270,14 +2618,18 @@
           <t>Es un profesor agradable.</t>
         </is>
       </c>
-      <c r="E64" s="7" t="n"/>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F64" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G64" s="7" t="n"/>
       <c r="H64" s="7" t="n"/>
     </row>
-    <row r="65">
+    <row r="65" ht="16" customHeight="1">
       <c r="A65" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -2296,14 +2648,18 @@
           <t>Hombre culto.</t>
         </is>
       </c>
-      <c r="E65" s="7" t="n"/>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F65" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G65" s="7" t="n"/>
       <c r="H65" s="7" t="n"/>
     </row>
-    <row r="66">
+    <row r="66" ht="32" customHeight="1">
       <c r="A66" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -2322,14 +2678,18 @@
           <t>Es muy bueno en diseño de compiladores. Creo que es uno de los mejores en este curso</t>
         </is>
       </c>
-      <c r="E66" s="7" t="n"/>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F66" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G66" s="7" t="n"/>
       <c r="H66" s="7" t="n"/>
     </row>
-    <row r="67">
+    <row r="67" ht="16" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -2348,14 +2708,18 @@
           <t>es un profesor nuevo en nuestra universidad, pero es un muy buen profesor.</t>
         </is>
       </c>
-      <c r="E67" s="7" t="n"/>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F67" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G67" s="7" t="n"/>
       <c r="H67" s="7" t="n"/>
     </row>
-    <row r="68">
+    <row r="68" ht="16" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -2374,14 +2738,18 @@
           <t>Gran profesor</t>
         </is>
       </c>
-      <c r="E68" s="7" t="n"/>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F68" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G68" s="7" t="n"/>
       <c r="H68" s="7" t="n"/>
     </row>
-    <row r="69">
+    <row r="69" ht="16" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -2400,14 +2768,18 @@
           <t>Puntual</t>
         </is>
       </c>
-      <c r="E69" s="7" t="n"/>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F69" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G69" s="7" t="n"/>
       <c r="H69" s="7" t="n"/>
     </row>
-    <row r="70">
+    <row r="70" ht="16" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -2426,14 +2798,18 @@
           <t>Explica muy bien los temas.</t>
         </is>
       </c>
-      <c r="E70" s="7" t="n"/>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F70" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G70" s="7" t="n"/>
       <c r="H70" s="7" t="n"/>
     </row>
-    <row r="71">
+    <row r="71" ht="16" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -2452,14 +2828,18 @@
           <t>Profesor.</t>
         </is>
       </c>
-      <c r="E71" s="7" t="n"/>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F71" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G71" s="7" t="n"/>
       <c r="H71" s="7" t="n"/>
     </row>
-    <row r="72">
+    <row r="72" ht="32" customHeight="1">
       <c r="A72" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -2478,14 +2858,18 @@
           <t>Persona muy educada, culta y de buen comportamiento. Muy agradable y muy respetable como profesor.</t>
         </is>
       </c>
-      <c r="E72" s="7" t="n"/>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F72" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G72" s="7" t="n"/>
       <c r="H72" s="7" t="n"/>
     </row>
-    <row r="73">
+    <row r="73" ht="48" customHeight="1">
       <c r="A73" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -2504,14 +2888,18 @@
           <t>Es uno de los mejores profesores de aiub. Tiene muchos conocimientos y sabe cómo hacer que sus estudiantes aprendan más que solo los materiales de estudio.</t>
         </is>
       </c>
-      <c r="E73" s="7" t="n"/>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F73" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G73" s="7" t="n"/>
       <c r="H73" s="7" t="n"/>
     </row>
-    <row r="74">
+    <row r="74" ht="32" customHeight="1">
       <c r="A74" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -2530,14 +2918,22 @@
           <t>creo que no es tan bueno como se suponía que sería y espero que lo haga mejor la próxima vez.</t>
         </is>
       </c>
-      <c r="E74" s="7" t="n"/>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F74" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>critica_suave</t>
+        </is>
+      </c>
       <c r="H74" s="7" t="n"/>
     </row>
-    <row r="75">
+    <row r="75" ht="32" customHeight="1">
       <c r="A75" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -2556,14 +2952,22 @@
           <t>La situación actual es buena para nosotros; si AIUB organizara un curso básico de inglés para los estudiantes, nos sería aún más útil.</t>
         </is>
       </c>
-      <c r="E75" s="7" t="n"/>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F75" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>critica_suave</t>
+        </is>
+      </c>
       <c r="H75" s="7" t="n"/>
     </row>
-    <row r="76">
+    <row r="76" ht="16" customHeight="1">
       <c r="A76" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -2582,14 +2986,18 @@
           <t>Es el mejor en esta sección. Pero, profesor, sea constante.</t>
         </is>
       </c>
-      <c r="E76" s="7" t="n"/>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F76" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G76" s="7" t="n"/>
       <c r="H76" s="7" t="n"/>
     </row>
-    <row r="77">
+    <row r="77" ht="16" customHeight="1">
       <c r="A77" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -2608,14 +3016,18 @@
           <t>Es el profesor más cariñoso.</t>
         </is>
       </c>
-      <c r="E77" s="7" t="n"/>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F77" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G77" s="7" t="n"/>
       <c r="H77" s="7" t="n"/>
     </row>
-    <row r="78">
+    <row r="78" ht="16" customHeight="1">
       <c r="A78" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -2634,14 +3046,18 @@
           <t>Siempre esta bien preparado.</t>
         </is>
       </c>
-      <c r="E78" s="7" t="n"/>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F78" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G78" s="7" t="n"/>
       <c r="H78" s="7" t="n"/>
     </row>
-    <row r="79">
+    <row r="79" ht="16" customHeight="1">
       <c r="A79" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -2660,14 +3076,18 @@
           <t>Buen profesor. Fácil de entender</t>
         </is>
       </c>
-      <c r="E79" s="7" t="n"/>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F79" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G79" s="7" t="n"/>
       <c r="H79" s="7" t="n"/>
     </row>
-    <row r="80">
+    <row r="80" ht="16" customHeight="1">
       <c r="A80" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -2686,14 +3106,18 @@
           <t>Su estilo de enseñanza es de nivel B+.</t>
         </is>
       </c>
-      <c r="E80" s="7" t="n"/>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F80" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G80" s="7" t="n"/>
       <c r="H80" s="7" t="n"/>
     </row>
-    <row r="81">
+    <row r="81" ht="16" customHeight="1">
       <c r="A81" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -2712,14 +3136,18 @@
           <t>Realmente malo</t>
         </is>
       </c>
-      <c r="E81" s="7" t="n"/>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F81" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G81" s="7" t="n"/>
       <c r="H81" s="7" t="n"/>
     </row>
-    <row r="82">
+    <row r="82" ht="16" customHeight="1">
       <c r="A82" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -2738,14 +3166,22 @@
           <t>Ninguno.</t>
         </is>
       </c>
-      <c r="E82" s="7" t="n"/>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F82" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G82" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>sin_sentido</t>
+        </is>
+      </c>
       <c r="H82" s="7" t="n"/>
     </row>
-    <row r="83">
+    <row r="83" ht="32" customHeight="1">
       <c r="A83" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -2764,14 +3200,18 @@
           <t>su estilo de ensenanza es bueno. cada clase revisa, despues de ensenar, si entendimos el tema.</t>
         </is>
       </c>
-      <c r="E83" s="7" t="n"/>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F83" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83" s="7" t="n"/>
       <c r="H83" s="7" t="n"/>
     </row>
-    <row r="84">
+    <row r="84" ht="16" customHeight="1">
       <c r="A84" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -2790,14 +3230,18 @@
           <t>Es un profesor excelente.</t>
         </is>
       </c>
-      <c r="E84" s="7" t="n"/>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F84" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G84" s="7" t="n"/>
       <c r="H84" s="7" t="n"/>
     </row>
-    <row r="85">
+    <row r="85" ht="16" customHeight="1">
       <c r="A85" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -2816,14 +3260,18 @@
           <t>Tiene muy buen método de enseñanza.</t>
         </is>
       </c>
-      <c r="E85" s="7" t="n"/>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F85" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G85" s="7" t="n"/>
       <c r="H85" s="7" t="n"/>
     </row>
-    <row r="86">
+    <row r="86" ht="16" customHeight="1">
       <c r="A86" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -2842,14 +3290,18 @@
           <t>En general, es un buen profesor.</t>
         </is>
       </c>
-      <c r="E86" s="7" t="n"/>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F86" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G86" s="7" t="n"/>
       <c r="H86" s="7" t="n"/>
     </row>
-    <row r="87">
+    <row r="87" ht="16" customHeight="1">
       <c r="A87" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -2868,14 +3320,18 @@
           <t>El mejor</t>
         </is>
       </c>
-      <c r="E87" s="7" t="n"/>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F87" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G87" s="7" t="n"/>
       <c r="H87" s="7" t="n"/>
     </row>
-    <row r="88">
+    <row r="88" ht="16" customHeight="1">
       <c r="A88" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -2894,14 +3350,18 @@
           <t>no da puntos parciales</t>
         </is>
       </c>
-      <c r="E88" s="7" t="n"/>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F88" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G88" s="7" t="n"/>
       <c r="H88" s="7" t="n"/>
     </row>
-    <row r="89">
+    <row r="89" ht="32" customHeight="1">
       <c r="A89" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -2920,14 +3380,18 @@
           <t>entiendo la clase de la profesora, ella es capaz de aclarar nuestros conceptos sobre los temas de aprendizaje.</t>
         </is>
       </c>
-      <c r="E89" s="7" t="n"/>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F89" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G89" s="7" t="n"/>
       <c r="H89" s="7" t="n"/>
     </row>
-    <row r="90">
+    <row r="90" ht="16" customHeight="1">
       <c r="A90" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -2946,14 +3410,18 @@
           <t>Bueno.</t>
         </is>
       </c>
-      <c r="E90" s="7" t="n"/>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F90" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G90" s="7" t="n"/>
       <c r="H90" s="7" t="n"/>
     </row>
-    <row r="91">
+    <row r="91" ht="16" customHeight="1">
       <c r="A91" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -2972,14 +3440,18 @@
           <t>creo que es una buena profesora. Su método de enseñanza es bueno.</t>
         </is>
       </c>
-      <c r="E91" s="7" t="n"/>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F91" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G91" s="7" t="n"/>
       <c r="H91" s="7" t="n"/>
     </row>
-    <row r="92">
+    <row r="92" ht="16" customHeight="1">
       <c r="A92" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -2998,14 +3470,18 @@
           <t>Realmente es un profesor servicial.</t>
         </is>
       </c>
-      <c r="E92" s="7" t="n"/>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F92" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G92" s="7" t="n"/>
       <c r="H92" s="7" t="n"/>
     </row>
-    <row r="93">
+    <row r="93" ht="16" customHeight="1">
       <c r="A93" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -3024,14 +3500,18 @@
           <t>Excelente</t>
         </is>
       </c>
-      <c r="E93" s="7" t="n"/>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F93" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G93" s="7" t="n"/>
       <c r="H93" s="7" t="n"/>
     </row>
-    <row r="94">
+    <row r="94" ht="16" customHeight="1">
       <c r="A94" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -3050,14 +3530,18 @@
           <t>Excelentes habilidades.</t>
         </is>
       </c>
-      <c r="E94" s="7" t="n"/>
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F94" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G94" s="7" t="n"/>
       <c r="H94" s="7" t="n"/>
     </row>
-    <row r="95">
+    <row r="95" ht="32" customHeight="1">
       <c r="A95" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -3076,14 +3560,18 @@
           <t>Es un profesor bueno e inteligente. Nos enseña bien, pero lo único es que no nos da tantas calificaciones como quisiéramos.</t>
         </is>
       </c>
-      <c r="E95" s="7" t="n"/>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F95" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G95" s="7" t="n"/>
       <c r="H95" s="7" t="n"/>
     </row>
-    <row r="96">
+    <row r="96" ht="16" customHeight="1">
       <c r="A96" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -3102,14 +3590,22 @@
           <t>No tengo ningún comentario sobre él, porque no puedo entenderlo bien.</t>
         </is>
       </c>
-      <c r="E96" s="7" t="n"/>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F96" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G96" s="7" t="n"/>
+      <c r="G96" s="7" t="inlineStr">
+        <is>
+          <t>elogio_tibio</t>
+        </is>
+      </c>
       <c r="H96" s="7" t="n"/>
     </row>
-    <row r="97">
+    <row r="97" ht="16" customHeight="1">
       <c r="A97" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -3128,14 +3624,22 @@
           <t>Es un buen profesor, pero debería mejorar la interacción con los estudiantes</t>
         </is>
       </c>
-      <c r="E97" s="7" t="n"/>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F97" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G97" s="7" t="n"/>
+      <c r="G97" s="7" t="inlineStr">
+        <is>
+          <t>critica_suave</t>
+        </is>
+      </c>
       <c r="H97" s="7" t="n"/>
     </row>
-    <row r="98">
+    <row r="98" ht="32" customHeight="1">
       <c r="A98" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -3154,14 +3658,18 @@
           <t>Básicamente es agradable. Pero es demasiado estricto durante los exámenes. Y a veces es parcial con algunos estudiantes.</t>
         </is>
       </c>
-      <c r="E98" s="7" t="n"/>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F98" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G98" s="7" t="n"/>
       <c r="H98" s="7" t="n"/>
     </row>
-    <row r="99">
+    <row r="99" ht="16" customHeight="1">
       <c r="A99" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -3180,14 +3688,18 @@
           <t>es un profesor maravilloso. es el mejor, pero su voz es demasiado baja.</t>
         </is>
       </c>
-      <c r="E99" s="7" t="n"/>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F99" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G99" s="7" t="n"/>
       <c r="H99" s="7" t="n"/>
     </row>
-    <row r="100">
+    <row r="100" ht="16" customHeight="1">
       <c r="A100" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -3206,14 +3718,18 @@
           <t>una tontería.</t>
         </is>
       </c>
-      <c r="E100" s="7" t="n"/>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F100" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G100" s="7" t="n"/>
       <c r="H100" s="7" t="n"/>
     </row>
-    <row r="101">
+    <row r="101" ht="48" customHeight="1">
       <c r="A101" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -3232,14 +3748,18 @@
           <t>Creo que tiene buen conocimiento de computación, pero debería seguir las diapositivas o el libro. A veces no sabemos cómo debemos estudiar ni de dónde. Es un buen profesor.</t>
         </is>
       </c>
-      <c r="E101" s="7" t="n"/>
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F101" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G101" s="7" t="n"/>
       <c r="H101" s="7" t="n"/>
     </row>
-    <row r="102">
+    <row r="102" ht="16" customHeight="1">
       <c r="A102" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -3258,14 +3778,18 @@
           <t>Tiene conocimientos limitados sobre este curso.</t>
         </is>
       </c>
-      <c r="E102" s="7" t="n"/>
+      <c r="E102" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F102" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G102" s="7" t="n"/>
       <c r="H102" s="7" t="n"/>
     </row>
-    <row r="103">
+    <row r="103" ht="32" customHeight="1">
       <c r="A103" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -3284,14 +3808,18 @@
           <t>Su estilo de enseñanza no es muy bueno y los estudiantes no sienten interés por esta materia.</t>
         </is>
       </c>
-      <c r="E103" s="7" t="n"/>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F103" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G103" s="7" t="n"/>
       <c r="H103" s="7" t="n"/>
     </row>
-    <row r="104">
+    <row r="104" ht="16" customHeight="1">
       <c r="A104" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -3310,14 +3838,18 @@
           <t>Está bien.</t>
         </is>
       </c>
-      <c r="E104" s="7" t="n"/>
+      <c r="E104" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F104" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G104" s="7" t="n"/>
       <c r="H104" s="7" t="n"/>
     </row>
-    <row r="105">
+    <row r="105" ht="16" customHeight="1">
       <c r="A105" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -3336,14 +3868,22 @@
           <t>gracias</t>
         </is>
       </c>
-      <c r="E105" s="7" t="n"/>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F105" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G105" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G105" s="7" t="inlineStr">
+        <is>
+          <t>muy_corto</t>
+        </is>
+      </c>
       <c r="H105" s="7" t="n"/>
     </row>
-    <row r="106">
+    <row r="106" ht="16" customHeight="1">
       <c r="A106" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -3362,14 +3902,18 @@
           <t>Lo quiero y él nos quiere. El profesor Obaidul es muy buen profesor.</t>
         </is>
       </c>
-      <c r="E106" s="7" t="n"/>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F106" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G106" s="7" t="n"/>
       <c r="H106" s="7" t="n"/>
     </row>
-    <row r="107">
+    <row r="107" ht="16" customHeight="1">
       <c r="A107" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -3388,14 +3932,18 @@
           <t>Muy listo</t>
         </is>
       </c>
-      <c r="E107" s="7" t="n"/>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F107" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G107" s="7" t="n"/>
       <c r="H107" s="7" t="n"/>
     </row>
-    <row r="108">
+    <row r="108" ht="16" customHeight="1">
       <c r="A108" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -3414,14 +3962,22 @@
           <t>Se esfuerza al máximo, pero los estudiantes no logran aprender del todo.</t>
         </is>
       </c>
-      <c r="E108" s="7" t="n"/>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F108" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G108" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G108" s="7" t="inlineStr">
+        <is>
+          <t>critica_suave</t>
+        </is>
+      </c>
       <c r="H108" s="7" t="n"/>
     </row>
-    <row r="109">
+    <row r="109" ht="32" customHeight="1">
       <c r="A109" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -3440,14 +3996,18 @@
           <t>Es un buen tipo, pero hay un problema con el. A veces agranda mucho las cosas pequeñas. Aun asi, es un muy buen profesor.</t>
         </is>
       </c>
-      <c r="E109" s="7" t="n"/>
+      <c r="E109" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F109" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G109" s="7" t="n"/>
       <c r="H109" s="7" t="n"/>
     </row>
-    <row r="110">
+    <row r="110" ht="16" customHeight="1">
       <c r="A110" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -3466,14 +4026,18 @@
           <t>Es un profesor bien entrenado.</t>
         </is>
       </c>
-      <c r="E110" s="7" t="n"/>
+      <c r="E110" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F110" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G110" s="7" t="n"/>
       <c r="H110" s="7" t="n"/>
     </row>
-    <row r="111">
+    <row r="111" ht="16" customHeight="1">
       <c r="A111" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -3492,14 +4056,22 @@
           <t>Es un robot.</t>
         </is>
       </c>
-      <c r="E111" s="7" t="n"/>
+      <c r="E111" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F111" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G111" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G111" s="7" t="inlineStr">
+        <is>
+          <t>sin_sentido</t>
+        </is>
+      </c>
       <c r="H111" s="7" t="n"/>
     </row>
-    <row r="112">
+    <row r="112" ht="48" customHeight="1">
       <c r="A112" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -3518,14 +4090,22 @@
           <t>Es un profesor excelente, pero su método de enseñanza es muy difícil. Por ejemplo, su sistema de exámenes sorpresa a menudo perjudica nuestra calificación.</t>
         </is>
       </c>
-      <c r="E112" s="7" t="n"/>
+      <c r="E112" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F112" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G112" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G112" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H112" s="7" t="n"/>
     </row>
-    <row r="113">
+    <row r="113" ht="32" customHeight="1">
       <c r="A113" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -3544,14 +4124,22 @@
           <t>Es una buena persona y tambien un buen profesor, pero su comportamiento no es muy bueno.</t>
         </is>
       </c>
-      <c r="E113" s="7" t="n"/>
+      <c r="E113" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F113" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G113" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G113" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H113" s="7" t="n"/>
     </row>
-    <row r="114">
+    <row r="114" ht="16" customHeight="1">
       <c r="A114" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -3570,14 +4158,18 @@
           <t>es el mejor profesor.</t>
         </is>
       </c>
-      <c r="E114" s="7" t="n"/>
+      <c r="E114" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F114" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G114" s="7" t="n"/>
       <c r="H114" s="7" t="n"/>
     </row>
-    <row r="115">
+    <row r="115" ht="16" customHeight="1">
       <c r="A115" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -3596,14 +4188,18 @@
           <t>Tiene una personalidad agradable. Explica las cosas de una manera muy loable.</t>
         </is>
       </c>
-      <c r="E115" s="7" t="n"/>
+      <c r="E115" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F115" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G115" s="7" t="n"/>
       <c r="H115" s="7" t="n"/>
     </row>
-    <row r="116">
+    <row r="116" ht="16" customHeight="1">
       <c r="A116" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -3622,14 +4218,18 @@
           <t>Me cae bien por su inteligencia y su buen comportamiento.</t>
         </is>
       </c>
-      <c r="E116" s="7" t="n"/>
+      <c r="E116" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F116" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G116" s="7" t="n"/>
       <c r="H116" s="7" t="n"/>
     </row>
-    <row r="117">
+    <row r="117" ht="32" customHeight="1">
       <c r="A117" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -3648,14 +4248,18 @@
           <t>Lo que intenta hacernos entender, nunca lo comprendemos por su forma de hablar.</t>
         </is>
       </c>
-      <c r="E117" s="7" t="n"/>
+      <c r="E117" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F117" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G117" s="7" t="n"/>
       <c r="H117" s="7" t="n"/>
     </row>
-    <row r="118">
+    <row r="118" ht="32" customHeight="1">
       <c r="A118" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -3674,14 +4278,22 @@
           <t>creo que es una buena profesora. hace todo lo posible para que las lecciones nos queden claras. pero a la mayoría de nosotros no.</t>
         </is>
       </c>
-      <c r="E118" s="7" t="n"/>
+      <c r="E118" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F118" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G118" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G118" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H118" s="7" t="n"/>
     </row>
-    <row r="119">
+    <row r="119" ht="16" customHeight="1">
       <c r="A119" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -3700,14 +4312,18 @@
           <t>Explica teorias complejas de una manera facil.</t>
         </is>
       </c>
-      <c r="E119" s="7" t="n"/>
+      <c r="E119" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F119" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G119" s="7" t="n"/>
       <c r="H119" s="7" t="n"/>
     </row>
-    <row r="120">
+    <row r="120" ht="16" customHeight="1">
       <c r="A120" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -3726,14 +4342,18 @@
           <t>Es un buen profesor. Creo que AIUB necesita este tipo de profesores.</t>
         </is>
       </c>
-      <c r="E120" s="7" t="n"/>
+      <c r="E120" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F120" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G120" s="7" t="n"/>
       <c r="H120" s="7" t="n"/>
     </row>
-    <row r="121">
+    <row r="121" ht="16" customHeight="1">
       <c r="A121" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -3752,14 +4372,18 @@
           <t>Es un profesor con mucha experiencia y bueno.</t>
         </is>
       </c>
-      <c r="E121" s="7" t="n"/>
+      <c r="E121" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F121" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G121" s="7" t="n"/>
       <c r="H121" s="7" t="n"/>
     </row>
-    <row r="122">
+    <row r="122" ht="48" customHeight="1">
       <c r="A122" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -3778,14 +4402,18 @@
           <t>Es un buen profesor pero su voz es muy baja, lo que dificulta entender con claridad y también dificulta escuchar lo que dice. Aun así, sabe dar ejemplos y conceptos relevantes. Debería subir la voz.</t>
         </is>
       </c>
-      <c r="E122" s="7" t="n"/>
+      <c r="E122" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F122" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G122" s="7" t="n"/>
       <c r="H122" s="7" t="n"/>
     </row>
-    <row r="123">
+    <row r="123" ht="16" customHeight="1">
       <c r="A123" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -3804,14 +4432,18 @@
           <t>Los talleres son muy útiles para aprender.</t>
         </is>
       </c>
-      <c r="E123" s="7" t="n"/>
+      <c r="E123" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F123" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G123" s="7" t="n"/>
       <c r="H123" s="7" t="n"/>
     </row>
-    <row r="124">
+    <row r="124" ht="16" customHeight="1">
       <c r="A124" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -3830,14 +4462,18 @@
           <t>Es bueno enseñando. Pero</t>
         </is>
       </c>
-      <c r="E124" s="7" t="n"/>
+      <c r="E124" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F124" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G124" s="7" t="n"/>
       <c r="H124" s="7" t="n"/>
     </row>
-    <row r="125">
+    <row r="125" ht="16" customHeight="1">
       <c r="A125" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -3856,14 +4492,18 @@
           <t>mmm, es un buen profesor. Me gusta su enseñanza. :-)</t>
         </is>
       </c>
-      <c r="E125" s="7" t="n"/>
+      <c r="E125" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F125" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G125" s="7" t="n"/>
       <c r="H125" s="7" t="n"/>
     </row>
-    <row r="126">
+    <row r="126" ht="16" customHeight="1">
       <c r="A126" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -3882,14 +4522,18 @@
           <t>Es un buen profesor de finanzas.</t>
         </is>
       </c>
-      <c r="E126" s="7" t="n"/>
+      <c r="E126" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F126" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G126" s="7" t="n"/>
       <c r="H126" s="7" t="n"/>
     </row>
-    <row r="127">
+    <row r="127" ht="16" customHeight="1">
       <c r="A127" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -3908,14 +4552,18 @@
           <t>Es un buen profesor. Le deseo suerte.</t>
         </is>
       </c>
-      <c r="E127" s="7" t="n"/>
+      <c r="E127" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F127" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G127" s="7" t="n"/>
       <c r="H127" s="7" t="n"/>
     </row>
-    <row r="128">
+    <row r="128" ht="16" customHeight="1">
       <c r="A128" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -3934,14 +4582,22 @@
           <t>Más o menos.</t>
         </is>
       </c>
-      <c r="E128" s="7" t="n"/>
+      <c r="E128" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F128" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G128" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G128" s="7" t="inlineStr">
+        <is>
+          <t>muy_corto</t>
+        </is>
+      </c>
       <c r="H128" s="7" t="n"/>
     </row>
-    <row r="129">
+    <row r="129" ht="16" customHeight="1">
       <c r="A129" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -3960,14 +4616,18 @@
           <t>nos hace entender la materia muy claramente.</t>
         </is>
       </c>
-      <c r="E129" s="7" t="n"/>
+      <c r="E129" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F129" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G129" s="7" t="n"/>
       <c r="H129" s="7" t="n"/>
     </row>
-    <row r="130">
+    <row r="130" ht="16" customHeight="1">
       <c r="A130" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -3986,14 +4646,18 @@
           <t>es magnífico.</t>
         </is>
       </c>
-      <c r="E130" s="7" t="n"/>
+      <c r="E130" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F130" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G130" s="7" t="n"/>
       <c r="H130" s="7" t="n"/>
     </row>
-    <row r="131">
+    <row r="131" ht="48" customHeight="1">
       <c r="A131" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -4012,14 +4676,18 @@
           <t>Creo que tiene un enorme conocimiento de la materia de mi curso. Su comportamiento es simplemente relajado. Esa es la clave principal de cualquier profesor. Por eso aprendimos bien.</t>
         </is>
       </c>
-      <c r="E131" s="7" t="n"/>
+      <c r="E131" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F131" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G131" s="7" t="n"/>
       <c r="H131" s="7" t="n"/>
     </row>
-    <row r="132">
+    <row r="132" ht="16" customHeight="1">
       <c r="A132" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -4038,14 +4706,18 @@
           <t>Esta entre el punado de buenos profesores de EEE.</t>
         </is>
       </c>
-      <c r="E132" s="7" t="n"/>
+      <c r="E132" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F132" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G132" s="7" t="n"/>
       <c r="H132" s="7" t="n"/>
     </row>
-    <row r="133">
+    <row r="133" ht="16" customHeight="1">
       <c r="A133" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -4064,14 +4736,18 @@
           <t>El mejor profesor</t>
         </is>
       </c>
-      <c r="E133" s="7" t="n"/>
+      <c r="E133" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F133" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G133" s="7" t="n"/>
       <c r="H133" s="7" t="n"/>
     </row>
-    <row r="134">
+    <row r="134" ht="48" customHeight="1">
       <c r="A134" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -4090,14 +4766,18 @@
           <t>Quiere hacerlo mejor para ayudar a los estudiantes a mejorar su desempeño en clase y su conocimiento. Trata de identificar especialmente a los más lentos que no logran entender las materias. Por eso es un buen profesor.</t>
         </is>
       </c>
-      <c r="E134" s="7" t="n"/>
+      <c r="E134" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F134" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G134" s="7" t="n"/>
       <c r="H134" s="7" t="n"/>
     </row>
-    <row r="135">
+    <row r="135" ht="32" customHeight="1">
       <c r="A135" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -4116,14 +4796,18 @@
           <t>Buena persona con buen comportamiento, muy buen conocimiento de bases de datos y VB, con gran profundidad de conocimiento.</t>
         </is>
       </c>
-      <c r="E135" s="7" t="n"/>
+      <c r="E135" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F135" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G135" s="7" t="n"/>
       <c r="H135" s="7" t="n"/>
     </row>
-    <row r="136">
+    <row r="136" ht="16" customHeight="1">
       <c r="A136" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -4142,14 +4826,22 @@
           <t>Está dibujando.</t>
         </is>
       </c>
-      <c r="E136" s="7" t="n"/>
+      <c r="E136" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F136" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G136" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G136" s="7" t="inlineStr">
+        <is>
+          <t>sin_sentido</t>
+        </is>
+      </c>
       <c r="H136" s="7" t="n"/>
     </row>
-    <row r="137">
+    <row r="137" ht="16" customHeight="1">
       <c r="A137" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -4168,14 +4860,18 @@
           <t>Realmente es un buen profesor.</t>
         </is>
       </c>
-      <c r="E137" s="7" t="n"/>
+      <c r="E137" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F137" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G137" s="7" t="n"/>
       <c r="H137" s="7" t="n"/>
     </row>
-    <row r="138">
+    <row r="138" ht="32" customHeight="1">
       <c r="A138" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -4194,14 +4890,22 @@
           <t>Es un buen profesor. Debería explicar los experimentos de laboratorio, sus procedimientos y resultados de forma más detallada a los estudiantes.</t>
         </is>
       </c>
-      <c r="E138" s="7" t="n"/>
+      <c r="E138" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F138" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G138" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G138" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H138" s="7" t="n"/>
     </row>
-    <row r="139">
+    <row r="139" ht="16" customHeight="1">
       <c r="A139" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -4220,14 +4924,18 @@
           <t>Su forma de enseñar es realmente buena</t>
         </is>
       </c>
-      <c r="E139" s="7" t="n"/>
+      <c r="E139" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F139" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G139" s="7" t="n"/>
       <c r="H139" s="7" t="n"/>
     </row>
-    <row r="140">
+    <row r="140" ht="16" customHeight="1">
       <c r="A140" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -4246,14 +4954,18 @@
           <t>Es un buen profesor. Yo también lo apoyo.</t>
         </is>
       </c>
-      <c r="E140" s="7" t="n"/>
+      <c r="E140" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F140" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G140" s="7" t="n"/>
       <c r="H140" s="7" t="n"/>
     </row>
-    <row r="141">
+    <row r="141" ht="48" customHeight="1">
       <c r="A141" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -4272,14 +4984,18 @@
           <t>Ha sido muy efectivo y tiene un vasto conocimiento del tema. Es la persona indicada para impartir este curso; en una palabra, 'dinámico'. Debería mostrar un poco más su sonrisa.</t>
         </is>
       </c>
-      <c r="E141" s="7" t="n"/>
+      <c r="E141" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F141" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G141" s="7" t="n"/>
       <c r="H141" s="7" t="n"/>
     </row>
-    <row r="142">
+    <row r="142" ht="32" customHeight="1">
       <c r="A142" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -4298,14 +5014,18 @@
           <t>Es un gran profesor. Su desempeño es excelente. Nos enseña muy muy bien. En general es el mejor profesor.</t>
         </is>
       </c>
-      <c r="E142" s="7" t="n"/>
+      <c r="E142" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F142" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G142" s="7" t="n"/>
       <c r="H142" s="7" t="n"/>
     </row>
-    <row r="143">
+    <row r="143" ht="16" customHeight="1">
       <c r="A143" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -4324,14 +5044,18 @@
           <t>Es un profesor bueno y responsable.</t>
         </is>
       </c>
-      <c r="E143" s="7" t="n"/>
+      <c r="E143" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F143" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G143" s="7" t="n"/>
       <c r="H143" s="7" t="n"/>
     </row>
-    <row r="144">
+    <row r="144" ht="16" customHeight="1">
       <c r="A144" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -4350,14 +5074,22 @@
           <t>considérenos, por favor.</t>
         </is>
       </c>
-      <c r="E144" s="7" t="n"/>
+      <c r="E144" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F144" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G144" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G144" s="7" t="inlineStr">
+        <is>
+          <t>sin_sentido</t>
+        </is>
+      </c>
       <c r="H144" s="7" t="n"/>
     </row>
-    <row r="145">
+    <row r="145" ht="16" customHeight="1">
       <c r="A145" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -4376,14 +5108,18 @@
           <t>Mantiene un buen y adecuado horario de clases.</t>
         </is>
       </c>
-      <c r="E145" s="7" t="n"/>
+      <c r="E145" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F145" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G145" s="7" t="n"/>
       <c r="H145" s="7" t="n"/>
     </row>
-    <row r="146">
+    <row r="146" ht="16" customHeight="1">
       <c r="A146" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -4402,14 +5138,18 @@
           <t>Disfruto mucho su clase, porque la hace amena con buenos ejemplos.</t>
         </is>
       </c>
-      <c r="E146" s="7" t="n"/>
+      <c r="E146" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F146" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G146" s="7" t="n"/>
       <c r="H146" s="7" t="n"/>
     </row>
-    <row r="147">
+    <row r="147" ht="32" customHeight="1">
       <c r="A147" s="5" t="inlineStr">
         <is>
           <t>A1</t>
@@ -4428,2755 +5168,3237 @@
           <t>Es muy buen profesor. Me gusta mucho. Creo que la mayoría de los profesores deberían ser como Emdad</t>
         </is>
       </c>
-      <c r="E147" s="7" t="n"/>
+      <c r="E147" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F147" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G147" s="7" t="n"/>
       <c r="H147" s="7" t="n"/>
     </row>
-    <row r="148">
+    <row r="148" ht="16" customHeight="1">
       <c r="A148" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B148" s="5" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>A1-8541C5</t>
+          <t>A1-4ADBEB</t>
         </is>
       </c>
       <c r="D148" s="6" t="inlineStr">
         <is>
-          <t>gseb ndfg</t>
-        </is>
-      </c>
-      <c r="E148" s="7" t="n"/>
+          <t>Sabe todo sobre la materia, pero no puede enseñarnos adecuadamente.</t>
+        </is>
+      </c>
+      <c r="E148" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F148" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G148" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G148" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H148" s="7" t="n"/>
     </row>
-    <row r="149">
+    <row r="149" ht="16" customHeight="1">
       <c r="A149" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B149" s="5" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>A1-4ADBEB</t>
+          <t>A1-8231EE</t>
         </is>
       </c>
       <c r="D149" s="6" t="inlineStr">
         <is>
-          <t>Sabe todo sobre la materia, pero no puede enseñarnos adecuadamente.</t>
-        </is>
-      </c>
-      <c r="E149" s="7" t="n"/>
+          <t>es el mejor</t>
+        </is>
+      </c>
+      <c r="E149" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F149" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G149" s="7" t="n"/>
+      <c r="G149" s="7" t="inlineStr">
+        <is>
+          <t>muy_corto</t>
+        </is>
+      </c>
       <c r="H149" s="7" t="n"/>
     </row>
-    <row r="150">
+    <row r="150" ht="16" customHeight="1">
       <c r="A150" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B150" s="5" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>A1-8231EE</t>
+          <t>A1-614D8B</t>
         </is>
       </c>
       <c r="D150" s="6" t="inlineStr">
         <is>
-          <t>es el mejor</t>
-        </is>
-      </c>
-      <c r="E150" s="7" t="n"/>
+          <t>No tiene capacidad para enseñar a los estudiantes. Siempre pierde el tiempo en clase.</t>
+        </is>
+      </c>
+      <c r="E150" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F150" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G150" s="7" t="n"/>
       <c r="H150" s="7" t="n"/>
     </row>
-    <row r="151">
+    <row r="151" ht="32" customHeight="1">
       <c r="A151" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B151" s="5" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>A1-614D8B</t>
+          <t>A1-6846C2</t>
         </is>
       </c>
       <c r="D151" s="6" t="inlineStr">
         <is>
-          <t>No tiene capacidad para enseñar a los estudiantes. Siempre pierde el tiempo en clase.</t>
-        </is>
-      </c>
-      <c r="E151" s="7" t="n"/>
+          <t>agresiva en su forma de vestir y su actitud, desnuda (obscena e indecente), no es una profesora para enseñar, como una bailarina de striptease, baila en clase, muestra su cuerpo y siempre se presenta como una mujer provocativa, usa fotua (tan delgada que se ve realmente desnuda), los estudiantes sienten vergüenza de verla y temor de ver su cuerpo. pedimos a las autoridades que cambien su forma de vestir en clase. los estudiantes vienen a la universidad a aprender algo, no a ver a una mujer desnuda y desagradable en clase.</t>
+        </is>
+      </c>
+      <c r="E151" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F151" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G151" s="7" t="n"/>
+      <c r="G151" s="7" t="inlineStr">
+        <is>
+          <t>descriptivo</t>
+        </is>
+      </c>
       <c r="H151" s="7" t="n"/>
     </row>
-    <row r="152">
+    <row r="152" ht="112" customHeight="1">
       <c r="A152" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B152" s="5" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>A1-6846C2</t>
+          <t>A1-6F5721</t>
         </is>
       </c>
       <c r="D152" s="6" t="inlineStr">
         <is>
-          <t>agresiva en su forma de vestir y su actitud, desnuda (obscena e indecente), no es una profesora para enseñar, como una bailarina de striptease, baila en clase, muestra su cuerpo y siempre se presenta como una mujer provocativa, usa fotua (tan delgada que se ve realmente desnuda), los estudiantes sienten vergüenza de verla y temor de ver su cuerpo. pedimos a las autoridades que cambien su forma de vestir en clase. los estudiantes vienen a la universidad a aprender algo, no a ver a una mujer desnuda y desagradable en clase.</t>
-        </is>
-      </c>
-      <c r="E152" s="7" t="n"/>
+          <t>El profesor es agradable y amable, no hay nada de qué quejarse.</t>
+        </is>
+      </c>
+      <c r="E152" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F152" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G152" s="7" t="n"/>
       <c r="H152" s="7" t="n"/>
     </row>
-    <row r="153">
+    <row r="153" ht="16" customHeight="1">
       <c r="A153" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B153" s="5" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>A1-6F5721</t>
+          <t>A1-E02216</t>
         </is>
       </c>
       <c r="D153" s="6" t="inlineStr">
         <is>
-          <t>El profesor es agradable y amable, no hay nada de qué quejarse.</t>
-        </is>
-      </c>
-      <c r="E153" s="7" t="n"/>
+          <t>Necesitamos cada vez más docentes jóvenes. Por supuesto, tendrán la orientación de los docentes veteranos.</t>
+        </is>
+      </c>
+      <c r="E153" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F153" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G153" s="7" t="n"/>
       <c r="H153" s="7" t="n"/>
     </row>
-    <row r="154">
+    <row r="154" ht="32" customHeight="1">
       <c r="A154" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B154" s="5" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>A1-E02216</t>
+          <t>A1-E029CB</t>
         </is>
       </c>
       <c r="D154" s="6" t="inlineStr">
         <is>
-          <t>Necesitamos cada vez más docentes jóvenes. Por supuesto, tendrán la orientación de los docentes veteranos.</t>
-        </is>
-      </c>
-      <c r="E154" s="7" t="n"/>
+          <t>Es una buena profesora, pero debería desarrollar su técnica de enseñanza.</t>
+        </is>
+      </c>
+      <c r="E154" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F154" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G154" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G154" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H154" s="7" t="n"/>
     </row>
-    <row r="155">
+    <row r="155" ht="16" customHeight="1">
       <c r="A155" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B155" s="5" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>A1-E029CB</t>
+          <t>A1-D1DBA4</t>
         </is>
       </c>
       <c r="D155" s="6" t="inlineStr">
         <is>
-          <t>Es una buena profesora, pero debería desarrollar su técnica de enseñanza.</t>
-        </is>
-      </c>
-      <c r="E155" s="7" t="n"/>
+          <t>Creo que es un profesor de nivel promedio.</t>
+        </is>
+      </c>
+      <c r="E155" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F155" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G155" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G155" s="7" t="inlineStr">
+        <is>
+          <t>critica_suave</t>
+        </is>
+      </c>
       <c r="H155" s="7" t="n"/>
     </row>
-    <row r="156">
+    <row r="156" ht="16" customHeight="1">
       <c r="A156" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B156" s="5" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>A1-D1DBA4</t>
+          <t>A1-C03AE8</t>
         </is>
       </c>
       <c r="D156" s="6" t="inlineStr">
         <is>
-          <t>Creo que es un profesor de nivel promedio.</t>
-        </is>
-      </c>
-      <c r="E156" s="7" t="n"/>
+          <t>Es un profesor muy agradable.</t>
+        </is>
+      </c>
+      <c r="E156" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F156" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G156" s="7" t="n"/>
       <c r="H156" s="7" t="n"/>
     </row>
-    <row r="157">
+    <row r="157" ht="16" customHeight="1">
       <c r="A157" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B157" s="5" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>A1-C03AE8</t>
+          <t>A1-45EE2E</t>
         </is>
       </c>
       <c r="D157" s="6" t="inlineStr">
         <is>
-          <t>Es un profesor muy agradable.</t>
-        </is>
-      </c>
-      <c r="E157" s="7" t="n"/>
+          <t>Básicamente es agradable. Pero es demasiado estricto durante los exámenes. Y a veces es parcial con algunos estudiantes.</t>
+        </is>
+      </c>
+      <c r="E157" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F157" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G157" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G157" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H157" s="7" t="n"/>
     </row>
-    <row r="158">
+    <row r="158" ht="32" customHeight="1">
       <c r="A158" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B158" s="5" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>A1-45EE2E</t>
+          <t>A1-59C922</t>
         </is>
       </c>
       <c r="D158" s="6" t="inlineStr">
         <is>
-          <t>Básicamente es agradable. Pero es demasiado estricto durante los exámenes. Y a veces es parcial con algunos estudiantes.</t>
-        </is>
-      </c>
-      <c r="E158" s="7" t="n"/>
+          <t>Es un gran profesor.</t>
+        </is>
+      </c>
+      <c r="E158" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F158" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G158" s="7" t="n"/>
       <c r="H158" s="7" t="n"/>
     </row>
-    <row r="159">
+    <row r="159" ht="16" customHeight="1">
       <c r="A159" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B159" s="5" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>A1-59C922</t>
+          <t>A1-112110</t>
         </is>
       </c>
       <c r="D159" s="6" t="inlineStr">
         <is>
-          <t>Es un gran profesor.</t>
-        </is>
-      </c>
-      <c r="E159" s="7" t="n"/>
+          <t>Creo que es un buen profesor.</t>
+        </is>
+      </c>
+      <c r="E159" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F159" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G159" s="7" t="n"/>
       <c r="H159" s="7" t="n"/>
     </row>
-    <row r="160">
+    <row r="160" ht="16" customHeight="1">
       <c r="A160" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B160" s="5" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>A1-112110</t>
+          <t>A1-FFD892</t>
         </is>
       </c>
       <c r="D160" s="6" t="inlineStr">
         <is>
-          <t>Creo que es un buen profesor.</t>
-        </is>
-      </c>
-      <c r="E160" s="7" t="n"/>
+          <t>Bueno, pero a veces pierde la paciencia.</t>
+        </is>
+      </c>
+      <c r="E160" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F160" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G160" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G160" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H160" s="7" t="n"/>
     </row>
-    <row r="161">
+    <row r="161" ht="16" customHeight="1">
       <c r="A161" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B161" s="5" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>A1-FFD892</t>
+          <t>A1-4C7E7F</t>
         </is>
       </c>
       <c r="D161" s="6" t="inlineStr">
         <is>
-          <t>Bueno, pero a veces pierde la paciencia.</t>
-        </is>
-      </c>
-      <c r="E161" s="7" t="n"/>
+          <t>Es un profesor brillante y talentoso. Su comportamiento es muy bueno.</t>
+        </is>
+      </c>
+      <c r="E161" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F161" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G161" s="7" t="n"/>
       <c r="H161" s="7" t="n"/>
     </row>
-    <row r="162">
+    <row r="162" ht="16" customHeight="1">
       <c r="A162" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B162" s="5" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>A1-4C7E7F</t>
+          <t>A1-FD97D7</t>
         </is>
       </c>
       <c r="D162" s="6" t="inlineStr">
         <is>
-          <t>Es un profesor brillante y talentoso. Su comportamiento es muy bueno.</t>
-        </is>
-      </c>
-      <c r="E162" s="7" t="n"/>
+          <t>Enseña su lección de forma muy comprensible y es muy efectivo para el estudiante.</t>
+        </is>
+      </c>
+      <c r="E162" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F162" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G162" s="7" t="n"/>
       <c r="H162" s="7" t="n"/>
     </row>
-    <row r="163">
+    <row r="163" ht="32" customHeight="1">
       <c r="A163" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B163" s="5" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>A1-FD97D7</t>
+          <t>A1-69B4A7</t>
         </is>
       </c>
       <c r="D163" s="6" t="inlineStr">
         <is>
-          <t>Enseña su lección de forma muy comprensible y es muy efectivo para el estudiante.</t>
-        </is>
-      </c>
-      <c r="E163" s="7" t="n"/>
+          <t>No tan bueno. Él entiende todo, pero no se lo transmite al estudiante.</t>
+        </is>
+      </c>
+      <c r="E163" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F163" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G163" s="7" t="n"/>
       <c r="H163" s="7" t="n"/>
     </row>
-    <row r="164">
+    <row r="164" ht="16" customHeight="1">
       <c r="A164" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B164" s="5" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>A1-69B4A7</t>
+          <t>A1-18B905</t>
         </is>
       </c>
       <c r="D164" s="6" t="inlineStr">
         <is>
-          <t>No tan bueno. Él entiende todo, pero no se lo transmite al estudiante.</t>
-        </is>
-      </c>
-      <c r="E164" s="7" t="n"/>
+          <t>es un buen profesor y trata de ayudar a todos los estudiantes</t>
+        </is>
+      </c>
+      <c r="E164" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F164" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G164" s="7" t="n"/>
       <c r="H164" s="7" t="n"/>
     </row>
-    <row r="165">
+    <row r="165" ht="16" customHeight="1">
       <c r="A165" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B165" s="5" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>A1-18B905</t>
+          <t>A1-2C9366</t>
         </is>
       </c>
       <c r="D165" s="6" t="inlineStr">
         <is>
-          <t>es un buen profesor y trata de ayudar a todos los estudiantes</t>
-        </is>
-      </c>
-      <c r="E165" s="7" t="n"/>
+          <t>Puntual</t>
+        </is>
+      </c>
+      <c r="E165" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F165" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G165" s="7" t="n"/>
       <c r="H165" s="7" t="n"/>
     </row>
-    <row r="166">
+    <row r="166" ht="16" customHeight="1">
       <c r="A166" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B166" s="5" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>A1-2C9366</t>
+          <t>A1-C0EDE4</t>
         </is>
       </c>
       <c r="D166" s="6" t="inlineStr">
         <is>
-          <t>Puntual</t>
-        </is>
-      </c>
-      <c r="E166" s="7" t="n"/>
+          <t>Es una muy buena profesora.</t>
+        </is>
+      </c>
+      <c r="E166" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F166" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G166" s="7" t="n"/>
       <c r="H166" s="7" t="n"/>
     </row>
-    <row r="167">
+    <row r="167" ht="16" customHeight="1">
       <c r="A167" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B167" s="5" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>A1-C0EDE4</t>
+          <t>A1-E5354C</t>
         </is>
       </c>
       <c r="D167" s="6" t="inlineStr">
         <is>
-          <t>Es una muy buena profesora.</t>
-        </is>
-      </c>
-      <c r="E167" s="7" t="n"/>
+          <t>Es nuevo, pero es el mejor en economía.</t>
+        </is>
+      </c>
+      <c r="E167" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F167" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G167" s="7" t="n"/>
       <c r="H167" s="7" t="n"/>
     </row>
-    <row r="168">
+    <row r="168" ht="16" customHeight="1">
       <c r="A168" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B168" s="5" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>A1-E5354C</t>
+          <t>A1-E80150</t>
         </is>
       </c>
       <c r="D168" s="6" t="inlineStr">
         <is>
-          <t>Es nuevo, pero es el mejor en economía.</t>
-        </is>
-      </c>
-      <c r="E168" s="7" t="n"/>
+          <t>Bien.</t>
+        </is>
+      </c>
+      <c r="E168" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F168" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G168" s="7" t="n"/>
+      <c r="G168" s="7" t="inlineStr">
+        <is>
+          <t>muy_corto</t>
+        </is>
+      </c>
       <c r="H168" s="7" t="n"/>
     </row>
-    <row r="169">
+    <row r="169" ht="16" customHeight="1">
       <c r="A169" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B169" s="5" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>A1-E80150</t>
+          <t>A1-CF9863</t>
         </is>
       </c>
       <c r="D169" s="6" t="inlineStr">
         <is>
-          <t>Bien.</t>
-        </is>
-      </c>
-      <c r="E169" s="7" t="n"/>
+          <t>Desempeño promedio.</t>
+        </is>
+      </c>
+      <c r="E169" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F169" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G169" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G169" s="7" t="inlineStr">
+        <is>
+          <t>elogio_tibio</t>
+        </is>
+      </c>
       <c r="H169" s="7" t="n"/>
     </row>
-    <row r="170">
+    <row r="170" ht="16" customHeight="1">
       <c r="A170" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B170" s="5" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>A1-CF9863</t>
+          <t>A1-C7AAC1</t>
         </is>
       </c>
       <c r="D170" s="6" t="inlineStr">
         <is>
-          <t>Desempeño promedio.</t>
-        </is>
-      </c>
-      <c r="E170" s="7" t="n"/>
+          <t>Responsable.</t>
+        </is>
+      </c>
+      <c r="E170" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F170" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G170" s="7" t="n"/>
       <c r="H170" s="7" t="n"/>
     </row>
-    <row r="171">
+    <row r="171" ht="16" customHeight="1">
       <c r="A171" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B171" s="5" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>A1-C7AAC1</t>
+          <t>A1-7F5A76</t>
         </is>
       </c>
       <c r="D171" s="6" t="inlineStr">
         <is>
-          <t>Responsable.</t>
-        </is>
-      </c>
-      <c r="E171" s="7" t="n"/>
+          <t>¡Es realmente bueno!</t>
+        </is>
+      </c>
+      <c r="E171" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F171" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G171" s="7" t="n"/>
       <c r="H171" s="7" t="n"/>
     </row>
-    <row r="172">
+    <row r="172" ht="16" customHeight="1">
       <c r="A172" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B172" s="5" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>A1-7F5A76</t>
+          <t>A1-9CDD4F</t>
         </is>
       </c>
       <c r="D172" s="6" t="inlineStr">
         <is>
-          <t>¡Es realmente bueno!</t>
-        </is>
-      </c>
-      <c r="E172" s="7" t="n"/>
+          <t>Su forma sólida, segura y bien fundamentada de enseñar muestra claramente cuánto importa la experiencia. Aunque la física no es una materia central de mi carrera, creo que mis bases sobre una materia fundamental como la física deberían ser claras, y me considero afortunado de tenerlo como profesor. Mi única petición para él sería: "Profesor, nosotros, sus estudiantes, somos simples humanos y errar es humano, así que incluso con nuestro intento más sincero a veces terminamos cometiendo errores, y entonces solo nos queda esperar un poco de su clemencia. Realmente esperamos que sea amable como siempre y valore nuestros esfuerzos, gracias".</t>
+        </is>
+      </c>
+      <c r="E172" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F172" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G172" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G172" s="7" t="inlineStr">
+        <is>
+          <t>descriptivo</t>
+        </is>
+      </c>
       <c r="H172" s="7" t="n"/>
     </row>
-    <row r="173">
+    <row r="173" ht="144" customHeight="1">
       <c r="A173" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B173" s="5" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C173" s="5" t="inlineStr">
         <is>
-          <t>A1-9CDD4F</t>
+          <t>A1-34D1E4</t>
         </is>
       </c>
       <c r="D173" s="6" t="inlineStr">
         <is>
-          <t>Su forma sólida, segura y bien fundamentada de enseñar muestra claramente cuánto importa la experiencia. Aunque la física no es una materia central de mi carrera, creo que mis bases sobre una materia fundamental como la física deberían ser claras, y me considero afortunado de tenerlo como profesor. Mi única petición para él sería: "Profesor, nosotros, sus estudiantes, somos simples humanos y errar es humano, así que incluso con nuestro intento más sincero a veces terminamos cometiendo errores, y entonces solo nos queda esperar un poco de su clemencia. Realmente esperamos que sea amable como siempre y valore nuestros esfuerzos, gracias".</t>
-        </is>
-      </c>
-      <c r="E173" s="7" t="n"/>
+          <t>es un buen profesor y es muy servicial.</t>
+        </is>
+      </c>
+      <c r="E173" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F173" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G173" s="7" t="n"/>
       <c r="H173" s="7" t="n"/>
     </row>
-    <row r="174">
+    <row r="174" ht="16" customHeight="1">
       <c r="A174" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B174" s="5" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>A1-34D1E4</t>
+          <t>A1-E7724C</t>
         </is>
       </c>
       <c r="D174" s="6" t="inlineStr">
         <is>
-          <t>es un buen profesor y es muy servicial.</t>
-        </is>
-      </c>
-      <c r="E174" s="7" t="n"/>
+          <t>Es un muy buen profesor.</t>
+        </is>
+      </c>
+      <c r="E174" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F174" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G174" s="7" t="n"/>
       <c r="H174" s="7" t="n"/>
     </row>
-    <row r="175">
+    <row r="175" ht="16" customHeight="1">
       <c r="A175" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B175" s="5" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C175" s="5" t="inlineStr">
         <is>
-          <t>A1-E7724C</t>
+          <t>A1-601850</t>
         </is>
       </c>
       <c r="D175" s="6" t="inlineStr">
         <is>
-          <t>Es un muy buen profesor.</t>
-        </is>
-      </c>
-      <c r="E175" s="7" t="n"/>
+          <t>profesor brillante</t>
+        </is>
+      </c>
+      <c r="E175" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F175" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G175" s="7" t="n"/>
       <c r="H175" s="7" t="n"/>
     </row>
-    <row r="176">
+    <row r="176" ht="16" customHeight="1">
       <c r="A176" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B176" s="5" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>A1-601850</t>
+          <t>A1-9D209F</t>
         </is>
       </c>
       <c r="D176" s="6" t="inlineStr">
         <is>
-          <t>profesor brillante</t>
-        </is>
-      </c>
-      <c r="E176" s="7" t="n"/>
+          <t>Es un buen profesor. Sabe enseñar derecho comercial.</t>
+        </is>
+      </c>
+      <c r="E176" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F176" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G176" s="7" t="n"/>
       <c r="H176" s="7" t="n"/>
     </row>
-    <row r="177">
+    <row r="177" ht="16" customHeight="1">
       <c r="A177" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B177" s="5" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>A1-9D209F</t>
+          <t>A1-20C1F6</t>
         </is>
       </c>
       <c r="D177" s="6" t="inlineStr">
         <is>
-          <t>Es un buen profesor. Sabe enseñar derecho comercial.</t>
-        </is>
-      </c>
-      <c r="E177" s="7" t="n"/>
+          <t>Es bueno. Tiene algo en su actitud que realmente ayuda al estudiante a mantenerse en clase. Buen profesor.</t>
+        </is>
+      </c>
+      <c r="E177" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F177" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G177" s="7" t="n"/>
       <c r="H177" s="7" t="n"/>
     </row>
-    <row r="178">
+    <row r="178" ht="32" customHeight="1">
       <c r="A178" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B178" s="5" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>A1-20C1F6</t>
+          <t>A1-5F1E7E</t>
         </is>
       </c>
       <c r="D178" s="6" t="inlineStr">
         <is>
-          <t>Es bueno. Tiene algo en su actitud que realmente ayuda al estudiante a mantenerse en clase. Buen profesor.</t>
-        </is>
-      </c>
-      <c r="E178" s="7" t="n"/>
+          <t>Debería dar puntos extra.</t>
+        </is>
+      </c>
+      <c r="E178" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F178" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G178" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G178" s="7" t="inlineStr">
+        <is>
+          <t>critica_suave</t>
+        </is>
+      </c>
       <c r="H178" s="7" t="n"/>
     </row>
-    <row r="179">
+    <row r="179" ht="16" customHeight="1">
       <c r="A179" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B179" s="5" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C179" s="5" t="inlineStr">
         <is>
-          <t>A1-5F1E7E</t>
+          <t>A1-15A5AE</t>
         </is>
       </c>
       <c r="D179" s="6" t="inlineStr">
         <is>
-          <t>Debería dar puntos extra.</t>
-        </is>
-      </c>
-      <c r="E179" s="7" t="n"/>
+          <t>Debería tener más cuidado con los estudiantes al responderles de manera correcta. Debería modificar su política de exámenes porque está muy orientada a la teoría.</t>
+        </is>
+      </c>
+      <c r="E179" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F179" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G179" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G179" s="7" t="inlineStr">
+        <is>
+          <t>critica_suave</t>
+        </is>
+      </c>
       <c r="H179" s="7" t="n"/>
     </row>
-    <row r="180">
+    <row r="180" ht="48" customHeight="1">
       <c r="A180" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B180" s="5" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>A1-15A5AE</t>
+          <t>A1-92EF20</t>
         </is>
       </c>
       <c r="D180" s="6" t="inlineStr">
         <is>
-          <t>Debería tener más cuidado con los estudiantes al responderles de manera correcta. Debería modificar su política de exámenes porque está muy orientada a la teoría.</t>
-        </is>
-      </c>
-      <c r="E180" s="7" t="n"/>
+          <t>tiene amplio conocimiento, pero su estilo no es suficiente. las clases a veces son aburridas. pero es un buen profesor.</t>
+        </is>
+      </c>
+      <c r="E180" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F180" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G180" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G180" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H180" s="7" t="n"/>
     </row>
-    <row r="181">
+    <row r="181" ht="32" customHeight="1">
       <c r="A181" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B181" s="5" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C181" s="5" t="inlineStr">
         <is>
-          <t>A1-92EF20</t>
+          <t>A1-B5833D</t>
         </is>
       </c>
       <c r="D181" s="6" t="inlineStr">
         <is>
-          <t>tiene amplio conocimiento, pero su estilo no es suficiente. las clases a veces son aburridas. pero es un buen profesor.</t>
-        </is>
-      </c>
-      <c r="E181" s="7" t="n"/>
+          <t>Excelente profesor, muy claro.</t>
+        </is>
+      </c>
+      <c r="E181" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F181" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G181" s="7" t="n"/>
       <c r="H181" s="7" t="n"/>
     </row>
-    <row r="182">
+    <row r="182" ht="16" customHeight="1">
       <c r="A182" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B182" s="5" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>A1-B5833D</t>
+          <t>A1-E1AE01</t>
         </is>
       </c>
       <c r="D182" s="6" t="inlineStr">
         <is>
-          <t>Excelente profesor, muy claro.</t>
-        </is>
-      </c>
-      <c r="E182" s="7" t="n"/>
+          <t>No tiene suficiente confianza. Creo que debería capacitarse mejor. A veces confunde su material de enseñanza.</t>
+        </is>
+      </c>
+      <c r="E182" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F182" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G182" s="7" t="n"/>
       <c r="H182" s="7" t="n"/>
     </row>
-    <row r="183">
+    <row r="183" ht="32" customHeight="1">
       <c r="A183" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B183" s="5" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>A1-E1AE01</t>
+          <t>A1-6756C2</t>
         </is>
       </c>
       <c r="D183" s="6" t="inlineStr">
         <is>
-          <t>No tiene suficiente confianza. Creo que debería capacitarse mejor. A veces confunde su material de enseñanza.</t>
-        </is>
-      </c>
-      <c r="E183" s="7" t="n"/>
+          <t>Me cae muy bien. Siempre se preocupa por mí. Es muy amable.</t>
+        </is>
+      </c>
+      <c r="E183" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F183" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G183" s="7" t="n"/>
       <c r="H183" s="7" t="n"/>
     </row>
-    <row r="184">
+    <row r="184" ht="16" customHeight="1">
       <c r="A184" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B184" s="5" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>A1-6756C2</t>
+          <t>A1-7D7B41</t>
         </is>
       </c>
       <c r="D184" s="6" t="inlineStr">
         <is>
-          <t>Me cae muy bien. Siempre se preocupa por mí. Es muy amable.</t>
-        </is>
-      </c>
-      <c r="E184" s="7" t="n"/>
+          <t>Califica de forma injusta.</t>
+        </is>
+      </c>
+      <c r="E184" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F184" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G184" s="7" t="n"/>
       <c r="H184" s="7" t="n"/>
     </row>
-    <row r="185">
+    <row r="185" ht="16" customHeight="1">
       <c r="A185" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B185" s="5" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>A1-7D7B41</t>
+          <t>A1-D740A5</t>
         </is>
       </c>
       <c r="D185" s="6" t="inlineStr">
         <is>
-          <t>Califica de forma injusta.</t>
-        </is>
-      </c>
-      <c r="E185" s="7" t="n"/>
+          <t>No es mala para electrónica analógica.</t>
+        </is>
+      </c>
+      <c r="E185" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F185" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G185" s="7" t="n"/>
       <c r="H185" s="7" t="n"/>
     </row>
-    <row r="186">
+    <row r="186" ht="16" customHeight="1">
       <c r="A186" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B186" s="5" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>A1-D740A5</t>
+          <t>A1-881E5D</t>
         </is>
       </c>
       <c r="D186" s="6" t="inlineStr">
         <is>
-          <t>No es mala para electrónica analógica.</t>
-        </is>
-      </c>
-      <c r="E186" s="7" t="n"/>
+          <t>Es un buen profesor. Como estudiante de MBA, espero un comportamiento más profesional.</t>
+        </is>
+      </c>
+      <c r="E186" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F186" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G186" s="7" t="n"/>
       <c r="H186" s="7" t="n"/>
     </row>
-    <row r="187">
+    <row r="187" ht="32" customHeight="1">
       <c r="A187" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B187" s="5" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C187" s="5" t="inlineStr">
         <is>
-          <t>A1-881E5D</t>
+          <t>A1-156E23</t>
         </is>
       </c>
       <c r="D187" s="6" t="inlineStr">
         <is>
-          <t>Es un buen profesor. Como estudiante de MBA, espero un comportamiento más profesional.</t>
-        </is>
-      </c>
-      <c r="E187" s="7" t="n"/>
+          <t>Buena persona y nos enseña muy bien.</t>
+        </is>
+      </c>
+      <c r="E187" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F187" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G187" s="7" t="n"/>
       <c r="H187" s="7" t="n"/>
     </row>
-    <row r="188">
+    <row r="188" ht="16" customHeight="1">
       <c r="A188" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B188" s="5" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C188" s="5" t="inlineStr">
         <is>
-          <t>A1-156E23</t>
+          <t>A1-7DDBE8</t>
         </is>
       </c>
       <c r="D188" s="6" t="inlineStr">
         <is>
-          <t>Buena persona y nos enseña muy bien.</t>
-        </is>
-      </c>
-      <c r="E188" s="7" t="n"/>
+          <t>Muy buen profesor, pero deberia haber ensenado mas sobre la materia.</t>
+        </is>
+      </c>
+      <c r="E188" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F188" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G188" s="7" t="n"/>
       <c r="H188" s="7" t="n"/>
     </row>
-    <row r="189">
+    <row r="189" ht="16" customHeight="1">
       <c r="A189" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B189" s="5" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C189" s="5" t="inlineStr">
         <is>
-          <t>A1-7DDBE8</t>
+          <t>A1-EB1BA5</t>
         </is>
       </c>
       <c r="D189" s="6" t="inlineStr">
         <is>
-          <t>Muy buen profesor, pero deberia haber ensenado mas sobre la materia.</t>
-        </is>
-      </c>
-      <c r="E189" s="7" t="n"/>
+          <t>No es adecuado para todos los tipos de estudiantes. No logró motivar a los estudiantes débiles.</t>
+        </is>
+      </c>
+      <c r="E189" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F189" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G189" s="7" t="n"/>
       <c r="H189" s="7" t="n"/>
     </row>
-    <row r="190">
+    <row r="190" ht="32" customHeight="1">
       <c r="A190" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B190" s="5" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C190" s="5" t="inlineStr">
         <is>
-          <t>A1-EB1BA5</t>
+          <t>A1-557D29</t>
         </is>
       </c>
       <c r="D190" s="6" t="inlineStr">
         <is>
-          <t>No es adecuado para todos los tipos de estudiantes. No logró motivar a los estudiantes débiles.</t>
-        </is>
-      </c>
-      <c r="E190" s="7" t="n"/>
+          <t>Creo que tiene un enorme conocimiento de la materia de mi curso. Su comportamiento es simplemente relajado. Esa es la clave principal de cualquier profesor. Por eso aprendimos bien.</t>
+        </is>
+      </c>
+      <c r="E190" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F190" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G190" s="7" t="n"/>
       <c r="H190" s="7" t="n"/>
     </row>
-    <row r="191">
+    <row r="191" ht="48" customHeight="1">
       <c r="A191" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B191" s="5" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C191" s="5" t="inlineStr">
         <is>
-          <t>A1-557D29</t>
+          <t>A1-352C0E</t>
         </is>
       </c>
       <c r="D191" s="6" t="inlineStr">
         <is>
-          <t>Creo que tiene un enorme conocimiento de la materia de mi curso. Su comportamiento es simplemente relajado. Esa es la clave principal de cualquier profesor. Por eso aprendimos bien.</t>
-        </is>
-      </c>
-      <c r="E191" s="7" t="n"/>
+          <t>Es un buen profesor, pero debería preocuparse por los estudiantes que son débiles. Y prestar más atención a la calificación.</t>
+        </is>
+      </c>
+      <c r="E191" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F191" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G191" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G191" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H191" s="7" t="n"/>
     </row>
-    <row r="192">
+    <row r="192" ht="32" customHeight="1">
       <c r="A192" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B192" s="5" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C192" s="5" t="inlineStr">
         <is>
-          <t>A1-352C0E</t>
+          <t>A1-03253D</t>
         </is>
       </c>
       <c r="D192" s="6" t="inlineStr">
         <is>
-          <t>Es un buen profesor, pero debería preocuparse por los estudiantes que son débiles. Y prestar más atención a la calificación.</t>
-        </is>
-      </c>
-      <c r="E192" s="7" t="n"/>
+          <t>Está bien, pero no domina la materia. Otro problema es su forma de hablar.</t>
+        </is>
+      </c>
+      <c r="E192" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F192" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G192" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G192" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H192" s="7" t="n"/>
     </row>
-    <row r="193">
+    <row r="193" ht="16" customHeight="1">
       <c r="A193" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B193" s="5" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C193" s="5" t="inlineStr">
         <is>
-          <t>A1-03253D</t>
+          <t>A1-FAC8F0</t>
         </is>
       </c>
       <c r="D193" s="6" t="inlineStr">
         <is>
-          <t>Está bien, pero no domina la materia. Otro problema es su forma de hablar.</t>
-        </is>
-      </c>
-      <c r="E193" s="7" t="n"/>
+          <t>Es muy buen profesor y se asegura de que el estudiante haya entendido bien su lección.</t>
+        </is>
+      </c>
+      <c r="E193" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F193" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G193" s="7" t="n"/>
       <c r="H193" s="7" t="n"/>
     </row>
-    <row r="194">
+    <row r="194" ht="32" customHeight="1">
       <c r="A194" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B194" s="5" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C194" s="5" t="inlineStr">
         <is>
-          <t>A1-FAC8F0</t>
+          <t>A1-CE8A65</t>
         </is>
       </c>
       <c r="D194" s="6" t="inlineStr">
         <is>
-          <t>Es muy buen profesor y se asegura de que el estudiante haya entendido bien su lección.</t>
-        </is>
-      </c>
-      <c r="E194" s="7" t="n"/>
+          <t>Muy activo y deberia ser ascendido.</t>
+        </is>
+      </c>
+      <c r="E194" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F194" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G194" s="7" t="n"/>
       <c r="H194" s="7" t="n"/>
     </row>
-    <row r="195">
+    <row r="195" ht="16" customHeight="1">
       <c r="A195" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B195" s="5" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C195" s="5" t="inlineStr">
         <is>
-          <t>A1-CE8A65</t>
+          <t>A1-C86B54</t>
         </is>
       </c>
       <c r="D195" s="6" t="inlineStr">
         <is>
-          <t>Muy activo y deberia ser ascendido.</t>
-        </is>
-      </c>
-      <c r="E195" s="7" t="n"/>
+          <t>es muy agradable y todos disfrutamos su clase.</t>
+        </is>
+      </c>
+      <c r="E195" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F195" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G195" s="7" t="n"/>
       <c r="H195" s="7" t="n"/>
     </row>
-    <row r="196">
+    <row r="196" ht="16" customHeight="1">
       <c r="A196" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B196" s="5" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C196" s="5" t="inlineStr">
         <is>
-          <t>A1-C86B54</t>
+          <t>A1-F24928</t>
         </is>
       </c>
       <c r="D196" s="6" t="inlineStr">
         <is>
-          <t>es muy agradable y todos disfrutamos su clase.</t>
-        </is>
-      </c>
-      <c r="E196" s="7" t="n"/>
+          <t>Es una profesora agradable y tiene un buen método para hacer que la clase se entienda.</t>
+        </is>
+      </c>
+      <c r="E196" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F196" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G196" s="7" t="n"/>
       <c r="H196" s="7" t="n"/>
     </row>
-    <row r="197">
+    <row r="197" ht="32" customHeight="1">
       <c r="A197" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B197" s="5" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C197" s="5" t="inlineStr">
         <is>
-          <t>A1-F24928</t>
+          <t>A1-800A5B</t>
         </is>
       </c>
       <c r="D197" s="6" t="inlineStr">
         <is>
-          <t>Es una profesora agradable y tiene un buen método para hacer que la clase se entienda.</t>
-        </is>
-      </c>
-      <c r="E197" s="7" t="n"/>
+          <t>Sí, el estilo de enseñanza es bastante bueno y favorable. Debería desarrollarse más la interacción.</t>
+        </is>
+      </c>
+      <c r="E197" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F197" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G197" s="7" t="n"/>
       <c r="H197" s="7" t="n"/>
     </row>
-    <row r="198">
+    <row r="198" ht="32" customHeight="1">
       <c r="A198" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B198" s="5" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C198" s="5" t="inlineStr">
         <is>
-          <t>A1-800A5B</t>
+          <t>A1-6F88EB</t>
         </is>
       </c>
       <c r="D198" s="6" t="inlineStr">
         <is>
-          <t>Sí, el estilo de enseñanza es bastante bueno y favorable. Debería desarrollarse más la interacción.</t>
-        </is>
-      </c>
-      <c r="E198" s="7" t="n"/>
+          <t>Es un buen profesor que no regala calificaciones.</t>
+        </is>
+      </c>
+      <c r="E198" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F198" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G198" s="7" t="n"/>
       <c r="H198" s="7" t="n"/>
     </row>
-    <row r="199">
+    <row r="199" ht="16" customHeight="1">
       <c r="A199" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B199" s="5" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C199" s="5" t="inlineStr">
         <is>
-          <t>A1-6F88EB</t>
+          <t>A1-797E7B</t>
         </is>
       </c>
       <c r="D199" s="6" t="inlineStr">
         <is>
-          <t>Es un buen profesor que no regala calificaciones.</t>
-        </is>
-      </c>
-      <c r="E199" s="7" t="n"/>
+          <t>muy buen profesor</t>
+        </is>
+      </c>
+      <c r="E199" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F199" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G199" s="7" t="n"/>
       <c r="H199" s="7" t="n"/>
     </row>
-    <row r="200">
+    <row r="200" ht="16" customHeight="1">
       <c r="A200" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B200" s="5" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C200" s="5" t="inlineStr">
         <is>
-          <t>A1-797E7B</t>
+          <t>A1-74127C</t>
         </is>
       </c>
       <c r="D200" s="6" t="inlineStr">
         <is>
-          <t>muy buen profesor</t>
-        </is>
-      </c>
-      <c r="E200" s="7" t="n"/>
+          <t>Es bueno pero a veces su actitud se vuelve irritante, especialmente con los horarios de sus clases de recuperación o adicionales.</t>
+        </is>
+      </c>
+      <c r="E200" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F200" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G200" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G200" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H200" s="7" t="n"/>
     </row>
-    <row r="201">
+    <row r="201" ht="32" customHeight="1">
       <c r="A201" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B201" s="5" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C201" s="5" t="inlineStr">
         <is>
-          <t>A1-74127C</t>
+          <t>A1-011A0E</t>
         </is>
       </c>
       <c r="D201" s="6" t="inlineStr">
         <is>
-          <t>Es bueno pero a veces su actitud se vuelve irritante, especialmente con los horarios de sus clases de recuperación o adicionales.</t>
-        </is>
-      </c>
-      <c r="E201" s="7" t="n"/>
+          <t>siempre miente sobre su posición</t>
+        </is>
+      </c>
+      <c r="E201" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F201" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G201" s="7" t="n"/>
       <c r="H201" s="7" t="n"/>
     </row>
-    <row r="202">
+    <row r="202" ht="16" customHeight="1">
       <c r="A202" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B202" s="5" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C202" s="5" t="inlineStr">
         <is>
-          <t>A1-011A0E</t>
+          <t>A1-7C3754</t>
         </is>
       </c>
       <c r="D202" s="6" t="inlineStr">
         <is>
-          <t>siempre miente sobre su posición</t>
-        </is>
-      </c>
-      <c r="E202" s="7" t="n"/>
+          <t>Es una de las mejores profesoras de aiub. Ha mejorado mucho respecto al pasado. Su estilo de enseñanza, su política de exámenes y su comportamiento son simplemente buenos. Debería continuar así. Aprendemos algo de ella.</t>
+        </is>
+      </c>
+      <c r="E202" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F202" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G202" s="7" t="n"/>
       <c r="H202" s="7" t="n"/>
     </row>
-    <row r="203">
+    <row r="203" ht="48" customHeight="1">
       <c r="A203" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B203" s="5" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C203" s="5" t="inlineStr">
         <is>
-          <t>A1-7C3754</t>
+          <t>A1-D6B608</t>
         </is>
       </c>
       <c r="D203" s="6" t="inlineStr">
         <is>
-          <t>Es una de las mejores profesoras de aiub. Ha mejorado mucho respecto al pasado. Su estilo de enseñanza, su política de exámenes y su comportamiento son simplemente buenos. Debería continuar así. Aprendemos algo de ella.</t>
-        </is>
-      </c>
-      <c r="E203" s="7" t="n"/>
+          <t>Está bien, pero no excepcional.</t>
+        </is>
+      </c>
+      <c r="E203" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F203" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G203" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G203" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H203" s="7" t="n"/>
     </row>
-    <row r="204">
+    <row r="204" ht="16" customHeight="1">
       <c r="A204" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B204" s="5" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C204" s="5" t="inlineStr">
         <is>
-          <t>A1-D6B608</t>
+          <t>A1-7BB986</t>
         </is>
       </c>
       <c r="D204" s="6" t="inlineStr">
         <is>
-          <t>Está bien, pero no excepcional.</t>
-        </is>
-      </c>
-      <c r="E204" s="7" t="n"/>
+          <t>No es idóneo como docente de este curso.</t>
+        </is>
+      </c>
+      <c r="E204" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F204" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G204" s="7" t="n"/>
       <c r="H204" s="7" t="n"/>
     </row>
-    <row r="205">
+    <row r="205" ht="16" customHeight="1">
       <c r="A205" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B205" s="5" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C205" s="5" t="inlineStr">
         <is>
-          <t>A1-7BB986</t>
+          <t>A1-724016</t>
         </is>
       </c>
       <c r="D205" s="6" t="inlineStr">
         <is>
-          <t>No es idóneo como docente de este curso.</t>
-        </is>
-      </c>
-      <c r="E205" s="7" t="n"/>
+          <t>Es genial.</t>
+        </is>
+      </c>
+      <c r="E205" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F205" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G205" s="7" t="n"/>
       <c r="H205" s="7" t="n"/>
     </row>
-    <row r="206">
+    <row r="206" ht="16" customHeight="1">
       <c r="A206" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B206" s="5" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C206" s="5" t="inlineStr">
         <is>
-          <t>A1-724016</t>
+          <t>A1-9701A3</t>
         </is>
       </c>
       <c r="D206" s="6" t="inlineStr">
         <is>
-          <t>Es genial.</t>
-        </is>
-      </c>
-      <c r="E206" s="7" t="n"/>
+          <t>el material es difícil.</t>
+        </is>
+      </c>
+      <c r="E206" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F206" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G206" s="7" t="n"/>
       <c r="H206" s="7" t="n"/>
     </row>
-    <row r="207">
+    <row r="207" ht="16" customHeight="1">
       <c r="A207" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B207" s="5" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C207" s="5" t="inlineStr">
         <is>
-          <t>A1-9701A3</t>
+          <t>A1-EED0C8</t>
         </is>
       </c>
       <c r="D207" s="6" t="inlineStr">
         <is>
-          <t>el material es difícil.</t>
-        </is>
-      </c>
-      <c r="E207" s="7" t="n"/>
+          <t>Bien, pero debería ser más amigable.</t>
+        </is>
+      </c>
+      <c r="E207" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F207" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G207" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G207" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H207" s="7" t="n"/>
     </row>
-    <row r="208">
+    <row r="208" ht="16" customHeight="1">
       <c r="A208" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B208" s="5" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C208" s="5" t="inlineStr">
         <is>
-          <t>A1-EED0C8</t>
+          <t>A1-E9D8BF</t>
         </is>
       </c>
       <c r="D208" s="6" t="inlineStr">
         <is>
-          <t>Bien, pero debería ser más amigable.</t>
-        </is>
-      </c>
-      <c r="E208" s="7" t="n"/>
+          <t>Nada.</t>
+        </is>
+      </c>
+      <c r="E208" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F208" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G208" s="7" t="n"/>
       <c r="H208" s="7" t="n"/>
     </row>
-    <row r="209">
+    <row r="209" ht="16" customHeight="1">
       <c r="A209" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B209" s="5" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C209" s="5" t="inlineStr">
         <is>
-          <t>A1-E9D8BF</t>
+          <t>A1-C23534</t>
         </is>
       </c>
       <c r="D209" s="6" t="inlineStr">
         <is>
-          <t>Nada.</t>
-        </is>
-      </c>
-      <c r="E209" s="7" t="n"/>
+          <t>Ojalá pudiera quedarse para siempre. :(</t>
+        </is>
+      </c>
+      <c r="E209" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F209" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G209" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G209" s="7" t="inlineStr">
+        <is>
+          <t>sin_sentido</t>
+        </is>
+      </c>
       <c r="H209" s="7" t="n"/>
     </row>
-    <row r="210">
+    <row r="210" ht="16" customHeight="1">
       <c r="A210" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B210" s="5" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C210" s="5" t="inlineStr">
         <is>
-          <t>A1-C23534</t>
+          <t>A1-8324EB</t>
         </is>
       </c>
       <c r="D210" s="6" t="inlineStr">
         <is>
-          <t>Ojalá pudiera quedarse para siempre. :(</t>
-        </is>
-      </c>
-      <c r="E210" s="7" t="n"/>
+          <t>El profesor Shafiqul es mi profesor favorito favorito. Su estilo de enseñanza es muy bueno.</t>
+        </is>
+      </c>
+      <c r="E210" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F210" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G210" s="7" t="n"/>
       <c r="H210" s="7" t="n"/>
     </row>
-    <row r="211">
+    <row r="211" ht="32" customHeight="1">
       <c r="A211" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B211" s="5" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C211" s="5" t="inlineStr">
         <is>
-          <t>A1-8324EB</t>
+          <t>A1-39798D</t>
         </is>
       </c>
       <c r="D211" s="6" t="inlineStr">
         <is>
-          <t>El profesor Shafiqul es mi profesor favorito favorito. Su estilo de enseñanza es muy bueno.</t>
-        </is>
-      </c>
-      <c r="E211" s="7" t="n"/>
+          <t>Debes mejorar tu conocimiento.</t>
+        </is>
+      </c>
+      <c r="E211" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F211" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G211" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G211" s="7" t="inlineStr">
+        <is>
+          <t>critica_suave</t>
+        </is>
+      </c>
       <c r="H211" s="7" t="n"/>
     </row>
-    <row r="212">
+    <row r="212" ht="16" customHeight="1">
       <c r="A212" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B212" s="5" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C212" s="5" t="inlineStr">
         <is>
-          <t>A1-39798D</t>
+          <t>A1-FB28A2</t>
         </is>
       </c>
       <c r="D212" s="6" t="inlineStr">
         <is>
-          <t>Debes mejorar tu conocimiento.</t>
-        </is>
-      </c>
-      <c r="E212" s="7" t="n"/>
+          <t>Ayuda a entender la materia y a hacerla más fácil de comprender.</t>
+        </is>
+      </c>
+      <c r="E212" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F212" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G212" s="7" t="n"/>
       <c r="H212" s="7" t="n"/>
     </row>
-    <row r="213">
+    <row r="213" ht="16" customHeight="1">
       <c r="A213" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B213" s="5" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C213" s="5" t="inlineStr">
         <is>
-          <t>A1-FB28A2</t>
+          <t>A1-DD48D1</t>
         </is>
       </c>
       <c r="D213" s="6" t="inlineStr">
         <is>
-          <t>Ayuda a entender la materia y a hacerla más fácil de comprender.</t>
-        </is>
-      </c>
-      <c r="E213" s="7" t="n"/>
+          <t>Estoy orgulloso de ser estudiante de este profesor. Creo que Ghani, Md. Bayzid es un buen profesor por su buena enseñanza, comprensión, buen desempeño docente y buen comportamiento.</t>
+        </is>
+      </c>
+      <c r="E213" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F213" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G213" s="7" t="n"/>
       <c r="H213" s="7" t="n"/>
     </row>
-    <row r="214">
+    <row r="214" ht="48" customHeight="1">
       <c r="A214" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B214" s="5" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C214" s="5" t="inlineStr">
         <is>
-          <t>A1-DD48D1</t>
+          <t>A1-B9F431</t>
         </is>
       </c>
       <c r="D214" s="6" t="inlineStr">
         <is>
-          <t>Estoy orgulloso de ser estudiante de este profesor. Creo que Ghani, Md. Bayzid es un buen profesor por su buena enseñanza, comprensión, buen desempeño docente y buen comportamiento.</t>
-        </is>
-      </c>
-      <c r="E214" s="7" t="n"/>
+          <t>Puede que hayas olvidado de dónde te graduaste.</t>
+        </is>
+      </c>
+      <c r="E214" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F214" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G214" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G214" s="7" t="inlineStr">
+        <is>
+          <t>sin_sentido</t>
+        </is>
+      </c>
       <c r="H214" s="7" t="n"/>
     </row>
-    <row r="215">
+    <row r="215" ht="16" customHeight="1">
       <c r="A215" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B215" s="5" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C215" s="5" t="inlineStr">
         <is>
-          <t>A1-B9F431</t>
+          <t>A1-05D096</t>
         </is>
       </c>
       <c r="D215" s="6" t="inlineStr">
         <is>
-          <t>Puede que hayas olvidado de dónde te graduaste.</t>
-        </is>
-      </c>
-      <c r="E215" s="7" t="n"/>
+          <t>Me cae bien porque enseña bien el laboratorio y da buenas clases.</t>
+        </is>
+      </c>
+      <c r="E215" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F215" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G215" s="7" t="n"/>
       <c r="H215" s="7" t="n"/>
     </row>
-    <row r="216">
+    <row r="216" ht="16" customHeight="1">
       <c r="A216" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B216" s="5" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C216" s="5" t="inlineStr">
         <is>
-          <t>A1-05D096</t>
+          <t>A1-89EB6F</t>
         </is>
       </c>
       <c r="D216" s="6" t="inlineStr">
         <is>
-          <t>Me cae bien porque enseña bien el laboratorio y da buenas clases.</t>
-        </is>
-      </c>
-      <c r="E216" s="7" t="n"/>
+          <t>No está mal, pero tampoco tan bueno.</t>
+        </is>
+      </c>
+      <c r="E216" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F216" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G216" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G216" s="7" t="inlineStr">
+        <is>
+          <t>sin_sentido</t>
+        </is>
+      </c>
       <c r="H216" s="7" t="n"/>
     </row>
-    <row r="217">
+    <row r="217" ht="16" customHeight="1">
       <c r="A217" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B217" s="5" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C217" s="5" t="inlineStr">
         <is>
-          <t>A1-89EB6F</t>
+          <t>A1-9D6FD3</t>
         </is>
       </c>
       <c r="D217" s="6" t="inlineStr">
         <is>
-          <t>No está mal, pero tampoco tan bueno.</t>
-        </is>
-      </c>
-      <c r="E217" s="7" t="n"/>
+          <t>Necesita algo de conocimiento sobre enseñanza.</t>
+        </is>
+      </c>
+      <c r="E217" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F217" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G217" s="7" t="n"/>
       <c r="H217" s="7" t="n"/>
     </row>
-    <row r="218">
+    <row r="218" ht="16" customHeight="1">
       <c r="A218" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B218" s="5" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C218" s="5" t="inlineStr">
         <is>
-          <t>A1-9D6FD3</t>
+          <t>A1-AD3A4D</t>
         </is>
       </c>
       <c r="D218" s="6" t="inlineStr">
         <is>
-          <t>Necesita algo de conocimiento sobre enseñanza.</t>
-        </is>
-      </c>
-      <c r="E218" s="7" t="n"/>
+          <t>Es un buen profesor. Su forma de enseñar es excelente. Creo que es uno de los mejores profesores de AIUB.</t>
+        </is>
+      </c>
+      <c r="E218" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F218" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G218" s="7" t="n"/>
       <c r="H218" s="7" t="n"/>
     </row>
-    <row r="219">
+    <row r="219" ht="32" customHeight="1">
       <c r="A219" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B219" s="5" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C219" s="5" t="inlineStr">
         <is>
-          <t>A1-AD3A4D</t>
+          <t>A1-50EB3A</t>
         </is>
       </c>
       <c r="D219" s="6" t="inlineStr">
         <is>
-          <t>Es un buen profesor. Su forma de enseñar es excelente. Creo que es uno de los mejores profesores de AIUB.</t>
-        </is>
-      </c>
-      <c r="E219" s="7" t="n"/>
+          <t>Sin comentarios.</t>
+        </is>
+      </c>
+      <c r="E219" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F219" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G219" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G219" s="7" t="inlineStr">
+        <is>
+          <t>muy_corto</t>
+        </is>
+      </c>
       <c r="H219" s="7" t="n"/>
     </row>
-    <row r="220">
+    <row r="220" ht="16" customHeight="1">
       <c r="A220" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B220" s="5" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C220" s="5" t="inlineStr">
         <is>
-          <t>A1-50EB3A</t>
+          <t>A1-5853A3</t>
         </is>
       </c>
       <c r="D220" s="6" t="inlineStr">
         <is>
-          <t>Sin comentarios.</t>
-        </is>
-      </c>
-      <c r="E220" s="7" t="n"/>
+          <t>Es muy puntual para la clase.</t>
+        </is>
+      </c>
+      <c r="E220" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F220" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G220" s="7" t="n"/>
       <c r="H220" s="7" t="n"/>
     </row>
-    <row r="221">
+    <row r="221" ht="16" customHeight="1">
       <c r="A221" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B221" s="5" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C221" s="5" t="inlineStr">
         <is>
-          <t>A1-5853A3</t>
+          <t>A1-2428B6</t>
         </is>
       </c>
       <c r="D221" s="6" t="inlineStr">
         <is>
-          <t>Es muy puntual para la clase.</t>
-        </is>
-      </c>
-      <c r="E221" s="7" t="n"/>
+          <t>Muy bueno.</t>
+        </is>
+      </c>
+      <c r="E221" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F221" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G221" s="7" t="n"/>
       <c r="H221" s="7" t="n"/>
     </row>
-    <row r="222">
+    <row r="222" ht="16" customHeight="1">
       <c r="A222" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B222" s="5" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C222" s="5" t="inlineStr">
         <is>
-          <t>A1-2428B6</t>
+          <t>A1-59E25B</t>
         </is>
       </c>
       <c r="D222" s="6" t="inlineStr">
         <is>
-          <t>Muy bueno.</t>
-        </is>
-      </c>
-      <c r="E222" s="7" t="n"/>
+          <t>si hablo con honestidad, es un profesor realmente bueno para los conceptos de contabilidad; es cierto que tuvimos la mala suerte de no tenerlo desde el comienzo de este curso.</t>
+        </is>
+      </c>
+      <c r="E222" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F222" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G222" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G222" s="7" t="inlineStr">
+        <is>
+          <t>descriptivo</t>
+        </is>
+      </c>
       <c r="H222" s="7" t="n"/>
     </row>
-    <row r="223">
+    <row r="223" ht="48" customHeight="1">
       <c r="A223" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B223" s="5" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C223" s="5" t="inlineStr">
         <is>
-          <t>A1-59E25B</t>
+          <t>A1-CD6B6C</t>
         </is>
       </c>
       <c r="D223" s="6" t="inlineStr">
         <is>
-          <t>si hablo con honestidad, es un profesor realmente bueno para los conceptos de contabilidad; es cierto que tuvimos la mala suerte de no tenerlo desde el comienzo de este curso.</t>
-        </is>
-      </c>
-      <c r="E223" s="7" t="n"/>
+          <t>Es bueno.</t>
+        </is>
+      </c>
+      <c r="E223" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F223" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G223" s="7" t="n"/>
       <c r="H223" s="7" t="n"/>
     </row>
-    <row r="224">
+    <row r="224" ht="16" customHeight="1">
       <c r="A224" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B224" s="5" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C224" s="5" t="inlineStr">
         <is>
-          <t>A1-CD6B6C</t>
+          <t>A1-8AA742</t>
         </is>
       </c>
       <c r="D224" s="6" t="inlineStr">
         <is>
-          <t>Es bueno.</t>
-        </is>
-      </c>
-      <c r="E224" s="7" t="n"/>
+          <t>La profesora Usha es una gran persona.</t>
+        </is>
+      </c>
+      <c r="E224" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F224" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G224" s="7" t="n"/>
       <c r="H224" s="7" t="n"/>
     </row>
-    <row r="225">
+    <row r="225" ht="16" customHeight="1">
       <c r="A225" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B225" s="5" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C225" s="5" t="inlineStr">
         <is>
-          <t>A1-8AA742</t>
+          <t>A1-204D88</t>
         </is>
       </c>
       <c r="D225" s="6" t="inlineStr">
         <is>
-          <t>La profesora Usha es una gran persona.</t>
-        </is>
-      </c>
-      <c r="E225" s="7" t="n"/>
+          <t>si los estudiantes pudieran ver su examen de cuestionario y de parcial, entonces podrían entender sus errores y hacerlo bien en el final.</t>
+        </is>
+      </c>
+      <c r="E225" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F225" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G225" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G225" s="7" t="inlineStr">
+        <is>
+          <t>critica_suave</t>
+        </is>
+      </c>
       <c r="H225" s="7" t="n"/>
     </row>
-    <row r="226">
+    <row r="226" ht="32" customHeight="1">
       <c r="A226" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B226" s="5" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C226" s="5" t="inlineStr">
         <is>
-          <t>A1-204D88</t>
+          <t>A1-7F5B00</t>
         </is>
       </c>
       <c r="D226" s="6" t="inlineStr">
         <is>
-          <t>si los estudiantes pudieran ver su examen de cuestionario y de parcial, entonces podrían entender sus errores y hacerlo bien en el final.</t>
-        </is>
-      </c>
-      <c r="E226" s="7" t="n"/>
+          <t>Para hacer entender las matemáticas de forma más fácil y sencilla, trata de poner al estudiante en la mejor posición.</t>
+        </is>
+      </c>
+      <c r="E226" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F226" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G226" s="7" t="n"/>
       <c r="H226" s="7" t="n"/>
     </row>
-    <row r="227">
+    <row r="227" ht="32" customHeight="1">
       <c r="A227" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B227" s="5" t="n">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C227" s="5" t="inlineStr">
         <is>
-          <t>A1-7F5B00</t>
+          <t>A1-8A7D62</t>
         </is>
       </c>
       <c r="D227" s="6" t="inlineStr">
         <is>
-          <t>Para hacer entender las matemáticas de forma más fácil y sencilla, trata de poner al estudiante en la mejor posición.</t>
-        </is>
-      </c>
-      <c r="E227" s="7" t="n"/>
+          <t>Su conocimiento sobre este tema es bueno. Pero a veces no entendemos. El 50% de los estudiantes viene del departamento de ciencias. Es difícil de entender.</t>
+        </is>
+      </c>
+      <c r="E227" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F227" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G227" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G227" s="7" t="inlineStr">
+        <is>
+          <t>critica_suave</t>
+        </is>
+      </c>
       <c r="H227" s="7" t="n"/>
     </row>
-    <row r="228">
+    <row r="228" ht="32" customHeight="1">
       <c r="A228" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B228" s="5" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C228" s="5" t="inlineStr">
         <is>
-          <t>A1-DAA81D</t>
+          <t>A1-E98657</t>
         </is>
       </c>
       <c r="D228" s="6" t="inlineStr">
         <is>
-          <t>fgfhdo kruyriewto87to87ruirtrierui rfiuoe yreg irye ire iid ore oy iierw ie re yror yuryureyoiryoe</t>
-        </is>
-      </c>
-      <c r="E228" s="7" t="n"/>
+          <t>Profesor excelente</t>
+        </is>
+      </c>
+      <c r="E228" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F228" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G228" s="7" t="n"/>
       <c r="H228" s="7" t="n"/>
     </row>
-    <row r="229">
+    <row r="229" ht="48" customHeight="1">
       <c r="A229" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B229" s="5" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C229" s="5" t="inlineStr">
         <is>
-          <t>A1-8A7D62</t>
+          <t>A1-6235C0</t>
         </is>
       </c>
       <c r="D229" s="6" t="inlineStr">
         <is>
-          <t>Su conocimiento sobre este tema es bueno. Pero a veces no entendemos. El 50% de los estudiantes viene del departamento de ciencias. Es difícil de entender.</t>
-        </is>
-      </c>
-      <c r="E229" s="7" t="n"/>
+          <t>Es una profesora muy agradable. Estamos aprendiendo algo de ella.</t>
+        </is>
+      </c>
+      <c r="E229" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F229" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G229" s="7" t="n"/>
       <c r="H229" s="7" t="n"/>
     </row>
-    <row r="230">
+    <row r="230" ht="16" customHeight="1">
       <c r="A230" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B230" s="5" t="n">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C230" s="5" t="inlineStr">
         <is>
-          <t>A1-E98657</t>
+          <t>A1-71DC1F</t>
         </is>
       </c>
       <c r="D230" s="6" t="inlineStr">
         <is>
-          <t>Profesor excelente</t>
-        </is>
-      </c>
-      <c r="E230" s="7" t="n"/>
+          <t>Es muy bueno</t>
+        </is>
+      </c>
+      <c r="E230" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F230" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G230" s="7" t="n"/>
       <c r="H230" s="7" t="n"/>
     </row>
-    <row r="231">
+    <row r="231" ht="16" customHeight="1">
       <c r="A231" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B231" s="5" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C231" s="5" t="inlineStr">
         <is>
-          <t>A1-6235C0</t>
+          <t>A1-6B1948</t>
         </is>
       </c>
       <c r="D231" s="6" t="inlineStr">
         <is>
-          <t>Es una profesora muy agradable. Estamos aprendiendo algo de ella.</t>
-        </is>
-      </c>
-      <c r="E231" s="7" t="n"/>
+          <t>Es una buena profesora.</t>
+        </is>
+      </c>
+      <c r="E231" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F231" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G231" s="7" t="n"/>
       <c r="H231" s="7" t="n"/>
     </row>
-    <row r="232">
+    <row r="232" ht="16" customHeight="1">
       <c r="A232" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B232" s="5" t="n">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C232" s="5" t="inlineStr">
         <is>
-          <t>A1-71DC1F</t>
+          <t>A1-F5238B</t>
         </is>
       </c>
       <c r="D232" s="6" t="inlineStr">
         <is>
-          <t>Es muy bueno</t>
-        </is>
-      </c>
-      <c r="E232" s="7" t="n"/>
+          <t>el dr. bijoy bhushon das es un profesor para ser modelo a seguir de los estudiantes.</t>
+        </is>
+      </c>
+      <c r="E232" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F232" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G232" s="7" t="n"/>
       <c r="H232" s="7" t="n"/>
     </row>
-    <row r="233">
+    <row r="233" ht="16" customHeight="1">
       <c r="A233" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B233" s="5" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C233" s="5" t="inlineStr">
         <is>
-          <t>A1-6B1948</t>
+          <t>A1-788D8E</t>
         </is>
       </c>
       <c r="D233" s="6" t="inlineStr">
         <is>
-          <t>Es una buena profesora.</t>
-        </is>
-      </c>
-      <c r="E233" s="7" t="n"/>
+          <t>creo que debería ser más flexible y averiguar qué tipo de problemas enfrentan los estudiantes.</t>
+        </is>
+      </c>
+      <c r="E233" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F233" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G233" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G233" s="7" t="inlineStr">
+        <is>
+          <t>critica_suave</t>
+        </is>
+      </c>
       <c r="H233" s="7" t="n"/>
     </row>
-    <row r="234">
+    <row r="234" ht="32" customHeight="1">
       <c r="A234" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B234" s="5" t="n">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C234" s="5" t="inlineStr">
         <is>
-          <t>A1-F5238B</t>
+          <t>A1-BB9589</t>
         </is>
       </c>
       <c r="D234" s="6" t="inlineStr">
         <is>
-          <t>el dr. bijoy bhushon das es un profesor para ser modelo a seguir de los estudiantes.</t>
-        </is>
-      </c>
-      <c r="E234" s="7" t="n"/>
+          <t>Debería ser más comprensible.</t>
+        </is>
+      </c>
+      <c r="E234" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F234" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G234" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G234" s="7" t="inlineStr">
+        <is>
+          <t>critica_suave</t>
+        </is>
+      </c>
       <c r="H234" s="7" t="n"/>
     </row>
-    <row r="235">
+    <row r="235" ht="32" customHeight="1">
       <c r="A235" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B235" s="5" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C235" s="5" t="inlineStr">
         <is>
-          <t>A1-788D8E</t>
+          <t>A1-2239DF</t>
         </is>
       </c>
       <c r="D235" s="6" t="inlineStr">
         <is>
-          <t>creo que debería ser más flexible y averiguar qué tipo de problemas enfrentan los estudiantes.</t>
-        </is>
-      </c>
-      <c r="E235" s="7" t="n"/>
+          <t>El profesor es simplemente el mejor.</t>
+        </is>
+      </c>
+      <c r="E235" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F235" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G235" s="7" t="n"/>
       <c r="H235" s="7" t="n"/>
     </row>
-    <row r="236">
+    <row r="236" ht="16" customHeight="1">
       <c r="A236" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B236" s="5" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C236" s="5" t="inlineStr">
         <is>
-          <t>A1-BB9589</t>
+          <t>A1-FF9A72</t>
         </is>
       </c>
       <c r="D236" s="6" t="inlineStr">
         <is>
-          <t>Debería ser más comprensible.</t>
-        </is>
-      </c>
-      <c r="E236" s="7" t="n"/>
+          <t>Esta bien, pero siempre posterga las respuestas a las preguntas de los estudiantes sobre los materiales de estudio que no se entendieron.</t>
+        </is>
+      </c>
+      <c r="E236" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F236" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G236" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G236" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H236" s="7" t="n"/>
     </row>
-    <row r="237">
+    <row r="237" ht="16" customHeight="1">
       <c r="A237" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B237" s="5" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C237" s="5" t="inlineStr">
         <is>
-          <t>A1-2239DF</t>
+          <t>A1-8F0BF5</t>
         </is>
       </c>
       <c r="D237" s="6" t="inlineStr">
         <is>
-          <t>El profesor es simplemente el mejor.</t>
-        </is>
-      </c>
-      <c r="E237" s="7" t="n"/>
+          <t>No me gusta la política de la clase.</t>
+        </is>
+      </c>
+      <c r="E237" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F237" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G237" s="7" t="n"/>
       <c r="H237" s="7" t="n"/>
     </row>
-    <row r="238">
+    <row r="238" ht="32" customHeight="1">
       <c r="A238" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B238" s="5" t="n">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C238" s="5" t="inlineStr">
         <is>
-          <t>A1-FF9A72</t>
+          <t>A1-870E8E</t>
         </is>
       </c>
       <c r="D238" s="6" t="inlineStr">
         <is>
-          <t>Esta bien, pero siempre posterga las respuestas a las preguntas de los estudiantes sobre los materiales de estudio que no se entendieron.</t>
-        </is>
-      </c>
-      <c r="E238" s="7" t="n"/>
+          <t>No está mal.</t>
+        </is>
+      </c>
+      <c r="E238" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F238" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G238" s="7" t="n"/>
       <c r="H238" s="7" t="n"/>
     </row>
-    <row r="239">
+    <row r="239" ht="16" customHeight="1">
       <c r="A239" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B239" s="5" t="n">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C239" s="5" t="inlineStr">
         <is>
-          <t>A1-8F0BF5</t>
+          <t>A1-06A481</t>
         </is>
       </c>
       <c r="D239" s="6" t="inlineStr">
         <is>
-          <t>No me gusta la política de la clase.</t>
-        </is>
-      </c>
-      <c r="E239" s="7" t="n"/>
+          <t>Necesita mejorar.</t>
+        </is>
+      </c>
+      <c r="E239" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F239" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G239" s="7" t="n"/>
       <c r="H239" s="7" t="n"/>
     </row>
-    <row r="240">
+    <row r="240" ht="16" customHeight="1">
       <c r="A240" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B240" s="5" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C240" s="5" t="inlineStr">
         <is>
-          <t>A1-870E8E</t>
+          <t>A1-6ADA49</t>
         </is>
       </c>
       <c r="D240" s="6" t="inlineStr">
         <is>
-          <t>No está mal.</t>
-        </is>
-      </c>
-      <c r="E240" s="7" t="n"/>
+          <t>Esta bien, pero deberia aclarar mas sus materiales de clase, especialmente para los estudiantes de BBA.</t>
+        </is>
+      </c>
+      <c r="E240" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F240" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G240" s="7" t="n"/>
       <c r="H240" s="7" t="n"/>
     </row>
-    <row r="241">
+    <row r="241" ht="16" customHeight="1">
       <c r="A241" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B241" s="5" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C241" s="5" t="inlineStr">
         <is>
-          <t>A1-06A481</t>
+          <t>A1-F97225</t>
         </is>
       </c>
       <c r="D241" s="6" t="inlineStr">
         <is>
-          <t>Necesita mejorar.</t>
-        </is>
-      </c>
-      <c r="E241" s="7" t="n"/>
+          <t>Islam, M.M. Obaidul es eficaz, calificado, cooperativo y muy cercano a nosotros.</t>
+        </is>
+      </c>
+      <c r="E241" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F241" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G241" s="7" t="n"/>
       <c r="H241" s="7" t="n"/>
     </row>
-    <row r="242">
+    <row r="242" ht="32" customHeight="1">
       <c r="A242" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B242" s="5" t="n">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C242" s="5" t="inlineStr">
         <is>
-          <t>A1-6ADA49</t>
+          <t>A1-D6DFFA</t>
         </is>
       </c>
       <c r="D242" s="6" t="inlineStr">
         <is>
-          <t>Esta bien, pero deberia aclarar mas sus materiales de clase, especialmente para los estudiantes de BBA.</t>
-        </is>
-      </c>
-      <c r="E242" s="7" t="n"/>
+          <t>No tiene suficiente confianza. Creo que debería capacitarse mejor. A veces confunde su material de enseñanza.</t>
+        </is>
+      </c>
+      <c r="E242" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F242" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G242" s="7" t="n"/>
       <c r="H242" s="7" t="n"/>
     </row>
-    <row r="243">
+    <row r="243" ht="32" customHeight="1">
       <c r="A243" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B243" s="5" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C243" s="5" t="inlineStr">
         <is>
-          <t>A1-F97225</t>
+          <t>A1-8B3C6B</t>
         </is>
       </c>
       <c r="D243" s="6" t="inlineStr">
         <is>
-          <t>Islam, M.M. Obaidul es eficaz, calificado, cooperativo y muy cercano a nosotros.</t>
-        </is>
-      </c>
-      <c r="E243" s="7" t="n"/>
+          <t>El profesor nos da ejemplos de muy buena manera y motiva a los estudiantes, lo cual es algo bueno.</t>
+        </is>
+      </c>
+      <c r="E243" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F243" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G243" s="7" t="n"/>
       <c r="H243" s="7" t="n"/>
     </row>
-    <row r="244">
+    <row r="244" ht="32" customHeight="1">
       <c r="A244" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B244" s="5" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C244" s="5" t="inlineStr">
         <is>
-          <t>A1-D6DFFA</t>
+          <t>A1-83616D</t>
         </is>
       </c>
       <c r="D244" s="6" t="inlineStr">
         <is>
-          <t>No tiene suficiente confianza. Creo que debería capacitarse mejor. A veces confunde su material de enseñanza.</t>
-        </is>
-      </c>
-      <c r="E244" s="7" t="n"/>
+          <t>Es una buena persona.</t>
+        </is>
+      </c>
+      <c r="E244" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F244" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G244" s="7" t="n"/>
       <c r="H244" s="7" t="n"/>
     </row>
-    <row r="245">
+    <row r="245" ht="32" customHeight="1">
       <c r="A245" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B245" s="5" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C245" s="5" t="inlineStr">
         <is>
-          <t>A1-8B3C6B</t>
+          <t>A1-EBCD14</t>
         </is>
       </c>
       <c r="D245" s="6" t="inlineStr">
         <is>
-          <t>El profesor nos da ejemplos de muy buena manera y motiva a los estudiantes, lo cual es algo bueno.</t>
-        </is>
-      </c>
-      <c r="E245" s="7" t="n"/>
+          <t>gracias! esperaba tenerlo como profesor en algun curso. finalmente tuve la oportunidad de tener clase con usted.</t>
+        </is>
+      </c>
+      <c r="E245" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F245" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G245" s="7" t="n"/>
       <c r="H245" s="7" t="n"/>
     </row>
-    <row r="246">
+    <row r="246" ht="16" customHeight="1">
       <c r="A246" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B246" s="5" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C246" s="5" t="inlineStr">
         <is>
-          <t>A1-83616D</t>
+          <t>A1-21C2E9</t>
         </is>
       </c>
       <c r="D246" s="6" t="inlineStr">
         <is>
-          <t>Es una buena persona.</t>
-        </is>
-      </c>
-      <c r="E246" s="7" t="n"/>
+          <t>Necesita ser un poco más detallado en cuanto a la clase</t>
+        </is>
+      </c>
+      <c r="E246" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F246" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G246" s="7" t="n"/>
       <c r="H246" s="7" t="n"/>
     </row>
-    <row r="247">
+    <row r="247" ht="32" customHeight="1">
       <c r="A247" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B247" s="5" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C247" s="5" t="inlineStr">
         <is>
-          <t>A1-EBCD14</t>
+          <t>A1-F3AD37</t>
         </is>
       </c>
       <c r="D247" s="6" t="inlineStr">
         <is>
-          <t>gracias! esperaba tenerlo como profesor en algun curso. finalmente tuve la oportunidad de tener clase con usted.</t>
-        </is>
-      </c>
-      <c r="E247" s="7" t="n"/>
+          <t>es un profesor muy honesto.</t>
+        </is>
+      </c>
+      <c r="E247" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F247" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G247" s="7" t="n"/>
       <c r="H247" s="7" t="n"/>
     </row>
-    <row r="248">
+    <row r="248" ht="16" customHeight="1">
       <c r="A248" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B248" s="5" t="n">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C248" s="5" t="inlineStr">
         <is>
-          <t>A1-21C2E9</t>
+          <t>A1-FB76E9</t>
         </is>
       </c>
       <c r="D248" s="6" t="inlineStr">
         <is>
-          <t>Necesita ser un poco más detallado en cuanto a la clase</t>
-        </is>
-      </c>
-      <c r="E248" s="7" t="n"/>
+          <t>Es muy buen profesor para esta materia</t>
+        </is>
+      </c>
+      <c r="E248" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F248" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G248" s="7" t="n"/>
       <c r="H248" s="7" t="n"/>
     </row>
-    <row r="249">
+    <row r="249" ht="16" customHeight="1">
       <c r="A249" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B249" s="5" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C249" s="5" t="inlineStr">
         <is>
-          <t>A1-F3AD37</t>
+          <t>A1-16238A</t>
         </is>
       </c>
       <c r="D249" s="6" t="inlineStr">
         <is>
-          <t>es un profesor muy honesto.</t>
-        </is>
-      </c>
-      <c r="E249" s="7" t="n"/>
+          <t>es muy servicial y amigable, pero en la clase de laboratorio va muy rápido. si diera más tiempo a cada tema sería más útil</t>
+        </is>
+      </c>
+      <c r="E249" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F249" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G249" s="7" t="n"/>
       <c r="H249" s="7" t="n"/>
     </row>
-    <row r="250">
+    <row r="250" ht="16" customHeight="1">
       <c r="A250" s="5" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
       <c r="B250" s="5" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C250" s="5" t="inlineStr">
         <is>
-          <t>A1-FB76E9</t>
+          <t>A1-E77DB7</t>
         </is>
       </c>
       <c r="D250" s="6" t="inlineStr">
         <is>
-          <t>Es muy buen profesor para esta materia</t>
-        </is>
-      </c>
-      <c r="E250" s="7" t="n"/>
+          <t>Es buena</t>
+        </is>
+      </c>
+      <c r="E250" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F250" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G250" s="7" t="n"/>
       <c r="H250" s="7" t="n"/>
     </row>
-    <row r="251">
-      <c r="A251" s="5" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="B251" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="C251" s="5" t="inlineStr">
-        <is>
-          <t>A1-16238A</t>
-        </is>
-      </c>
-      <c r="D251" s="6" t="inlineStr">
-        <is>
-          <t>es muy servicial y amigable, pero en la clase de laboratorio va muy rápido. si diera más tiempo a cada tema sería más útil</t>
-        </is>
-      </c>
-      <c r="E251" s="7" t="n"/>
-      <c r="F251" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G251" s="7" t="n"/>
-      <c r="H251" s="7" t="n"/>
-    </row>
-    <row r="252">
-      <c r="A252" s="5" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="B252" s="5" t="n">
-        <v>251</v>
-      </c>
-      <c r="C252" s="5" t="inlineStr">
-        <is>
-          <t>A1-E77DB7</t>
-        </is>
-      </c>
-      <c r="D252" s="6" t="inlineStr">
-        <is>
-          <t>Es buena</t>
-        </is>
-      </c>
-      <c r="E252" s="7" t="n"/>
-      <c r="F252" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G252" s="7" t="n"/>
-      <c r="H252" s="7" t="n"/>
-    </row>
+    <row r="251" ht="32" customHeight="1"/>
+    <row r="252" ht="16" customHeight="1"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="0" password="8AE1"/>
   <dataValidations count="3">
-    <dataValidation sqref="E2:E252" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Etiqueta no válida" error="Elige POS, NEU o NEG." type="list">
-      <formula1>"POS,NEU,NEG"</formula1>
-    </dataValidation>
     <dataValidation sqref="F2:F252" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"0,1"</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G252" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"elogio_tibio,critica_suave,mixto_adversativa,descriptivo,muy_corto,sin_sentido,otro"</formula1>
     </dataValidation>
+    <dataValidation sqref="E2:E77 E79:E243 E245:E252" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Etiqueta no válida" error="Elige POS, NEU o NEG." type="list">
+      <formula1>"POS,NEU,NEG"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
